--- a/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
+++ b/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\initial_testing_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD74E64-3726-43B1-ADE8-10C04356B219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955480F1-46AE-483D-8E07-7507758AA321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="1" r:id="rId1"/>
@@ -280,13 +280,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -298,6 +297,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -584,12 +594,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="27" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27" style="11" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="11" customWidth="1"/>
     <col min="10" max="10" width="25.28515625" customWidth="1"/>
     <col min="11" max="11" width="15.7109375" customWidth="1"/>
     <col min="12" max="12" width="15.5703125" customWidth="1"/>
@@ -597,36 +607,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -634,22 +644,22 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="11">
         <v>0.79975124378109397</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="11">
         <v>0.88324175824175799</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="11">
         <v>0.83942558746736295</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="11">
         <v>0.78304612706701404</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="11">
         <v>0.56790237588980297</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="11">
         <v>0.573031189205507</v>
       </c>
     </row>
@@ -657,22 +667,22 @@
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="11">
         <v>0.82074263764404598</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="11">
         <v>0.88049450549450503</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="11">
         <v>0.84956925115970805</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="11">
         <v>0.80181604486479396</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="11">
         <v>0.60442987182720698</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="11">
         <v>0.60702436320925701</v>
       </c>
     </row>
@@ -680,49 +690,49 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="11">
         <v>0.82845744680850997</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="11">
         <v>0.85576923076922995</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="11">
         <v>0.84189189189189095</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="11">
         <v>0.79804678628208003</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="11">
         <v>0.59625862695241505</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="11">
         <v>0.59677049842303898</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="11">
         <v>0.81430219146482097</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="10">
         <v>0.969780219780219</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="10">
         <v>0.88526645768025003</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="13">
         <v>0.83331423242435398</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="10">
         <v>0.67138435366112903</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="10">
         <v>0.69332966827870102</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -736,22 +746,22 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="11">
         <v>0.78079710144927505</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="11">
         <v>0.59203296703296704</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="11">
         <v>0.67343750000000002</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="11">
         <v>0.65529513888888802</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="11">
         <v>0.32477469818058102</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="11">
         <v>0.33875378937587902</v>
       </c>
       <c r="J7" s="2" t="s">
@@ -766,22 +776,22 @@
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="11">
         <v>0.79928315412186302</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="11">
         <v>0.61263736263736202</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="11">
         <v>0.69362363919129</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="11">
         <v>0.67490955083473703</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="11">
         <v>0.36232377869585503</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="11">
         <v>0.37686930653137302</v>
       </c>
       <c r="J8" s="2" t="s">
@@ -796,22 +806,22 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="11">
         <v>0.80547112462005999</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="11">
         <v>0.72802197802197799</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="11">
         <v>0.76479076479076402</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="11">
         <v>0.72656364243362304</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="11">
         <v>0.45496942232390303</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="11">
         <v>0.45811749134135799</v>
       </c>
     </row>
@@ -819,22 +829,22 @@
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="11">
         <v>0.79880239520957996</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="11">
         <v>0.91620879120879095</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="11">
         <v>0.85348688419705698</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="11">
         <v>0.79498279767965596</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="11">
         <v>0.59339298647290994</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="11">
         <v>0.604401145582392</v>
       </c>
     </row>
@@ -842,22 +852,22 @@
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="11">
         <v>0.84036144578313199</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="11">
         <v>0.76648351648351598</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="11">
         <v>0.80172413793103403</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="11">
         <v>0.76816976127320902</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="11">
         <v>0.53764768118497597</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="11">
         <v>0.54076455696704495</v>
       </c>
     </row>
@@ -865,22 +875,22 @@
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="11">
         <v>0.87339743589743501</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="11">
         <v>0.74862637362637297</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="11">
         <v>0.80621301775147902</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="11">
         <v>0.78181021257944305</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="11">
         <v>0.56682909850330598</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="11">
         <v>0.57539884220945703</v>
       </c>
     </row>
@@ -888,22 +898,22 @@
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="11">
         <v>0.843653250773993</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="11">
         <v>0.74862637362637297</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="11">
         <v>0.79330422125181899</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="11">
         <v>0.76243660968073002</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="11">
         <v>0.52706078268109902</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="11">
         <v>0.53204455891968405</v>
       </c>
     </row>
@@ -911,22 +921,22 @@
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="11">
         <v>0.78571428571428503</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="11">
         <v>0.93681318681318604</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="11">
         <v>0.85463659147869597</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="11">
         <v>0.78856231487810402</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="11">
         <v>0.58324666729696495</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="11">
         <v>0.60261461928525195</v>
       </c>
     </row>
@@ -934,22 +944,22 @@
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="10">
         <v>0.87784090909090895</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="11">
         <v>0.84890109890109799</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="11">
         <v>0.86312849162011096</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="10">
         <v>0.83356424581005495</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="13">
         <v>0.667262330235882</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="11">
         <v>0.667816856359709</v>
       </c>
     </row>
@@ -957,22 +967,22 @@
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="11">
         <v>0.79761904761904701</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="11">
         <v>0.82829670329670302</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="11">
         <v>0.81266846361185896</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="11">
         <v>0.75970975923209005</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="11">
         <v>0.51968718741474895</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="11">
         <v>0.52029637344789303</v>
       </c>
     </row>
@@ -980,88 +990,85 @@
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="11">
         <v>0.75824175824175799</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="11">
         <v>0.66346153846153799</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="11">
         <v>0.70769230769230695</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="11">
         <v>0.666873332852714</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="11">
         <v>0.33751338125095498</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="11">
         <v>0.34143321028151502</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="4">
-        <f>MAX(B3:B17)</f>
+      <c r="B18" s="12">
+        <f t="shared" ref="B18:G18" si="0">MAX(B3:B17)</f>
         <v>0.87784090909090895</v>
       </c>
-      <c r="C18" s="4">
-        <f>MAX(C3:C17)</f>
+      <c r="C18" s="12">
+        <f t="shared" si="0"/>
         <v>0.969780219780219</v>
       </c>
-      <c r="D18" s="4">
-        <f>MAX(D3:D17)</f>
+      <c r="D18" s="12">
+        <f t="shared" si="0"/>
         <v>0.88526645768025003</v>
       </c>
-      <c r="E18" s="4">
-        <f>MAX(E3:E17)</f>
+      <c r="E18" s="12">
+        <f t="shared" si="0"/>
         <v>0.83356424581005495</v>
       </c>
-      <c r="F18" s="4">
-        <f>MAX(F3:F17)</f>
+      <c r="F18" s="12">
+        <f t="shared" si="0"/>
         <v>0.67138435366112903</v>
       </c>
-      <c r="G18" s="4">
-        <f>MAX(G3:G17)</f>
+      <c r="G18" s="12">
+        <f t="shared" si="0"/>
         <v>0.69332966827870102</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E19" s="3"/>
-    </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1069,22 +1076,22 @@
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="11">
         <v>0.62935323383084496</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="11">
         <v>0.88771929824561402</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="11">
         <v>0.73653566229985401</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="11">
         <v>0.69719032642402901</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="11">
         <v>0.41636436920596498</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="11">
         <v>0.44958683986051401</v>
       </c>
     </row>
@@ -1092,22 +1099,22 @@
       <c r="A23" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="11">
         <v>0.63252240717029395</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="11">
         <v>0.86666666666666603</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="11">
         <v>0.73131014063656496</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="11">
         <v>0.69775497781134399</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="11">
         <v>0.41339258660741302</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="11">
         <v>0.43974560639767402</v>
       </c>
     </row>
@@ -1115,22 +1122,22 @@
       <c r="A24" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="11">
         <v>0.63430851063829696</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="11">
         <v>0.83684210526315705</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="11">
         <v>0.721633888048411</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="11">
         <v>0.69505117825843898</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="11">
         <v>0.40356564019448898</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="11">
         <v>0.42235858766475398</v>
       </c>
     </row>
@@ -1138,22 +1145,22 @@
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="11">
         <v>0.62514417531718502</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="10">
         <v>0.95087719298245599</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="11">
         <v>0.75434933890048705</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="11">
         <v>0.69978773477687595</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="11">
         <v>0.43446480424551898</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="11">
         <v>0.49396627355914302</v>
       </c>
     </row>
@@ -1161,22 +1168,22 @@
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="11">
         <v>0.61231884057970998</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="11">
         <v>0.59298245614034994</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="11">
         <v>0.60249554367201397</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="11">
         <v>0.63101876420241898</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="11">
         <v>0.26220016542597102</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="11">
         <v>0.26231648271815899</v>
       </c>
     </row>
@@ -1184,22 +1191,22 @@
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="11">
         <v>0.62903225806451601</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="11">
         <v>0.61578947368421</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="11">
         <v>0.62234042553191404</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="11">
         <v>0.64782665448374799</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="11">
         <v>0.2957222566646</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="11">
         <v>0.29578046879019199</v>
       </c>
     </row>
@@ -1207,22 +1214,22 @@
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="11">
         <v>0.63677811550151897</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="11">
         <v>0.73508771929824501</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="11">
         <v>0.68241042345276803</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="11">
         <v>0.67924507883601803</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="11">
         <v>0.36183268562078102</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="11">
         <v>0.36564336078955301</v>
       </c>
     </row>
@@ -1230,22 +1237,22 @@
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="11">
         <v>0.62874251497005895</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="11">
         <v>0.92105263157894701</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="11">
         <v>0.74733096085409201</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="11">
         <v>0.70083198480873998</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="11">
         <v>0.42943244600703101</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="11">
         <v>0.47463559338419897</v>
       </c>
     </row>
@@ -1253,22 +1260,22 @@
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="11">
         <v>0.67319277108433695</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="11">
         <v>0.78421052631578902</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="11">
         <v>0.72447325769854098</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="11">
         <v>0.72033345689601502</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="11">
         <v>0.44399018806214202</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="11">
         <v>0.44933075746359702</v>
       </c>
     </row>
@@ -1276,22 +1283,22 @@
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="11">
         <v>0.6875</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="11">
         <v>0.75263157894736799</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="11">
         <v>0.71859296482412005</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="11">
         <v>0.72359373604695498</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="11">
         <v>0.44827586206896503</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="11">
         <v>0.45004857536801401</v>
       </c>
     </row>
@@ -1299,22 +1306,22 @@
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="11">
         <v>0.63467492260061897</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="11">
         <v>0.71929824561403499</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="11">
         <v>0.67434210526315697</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="11">
         <v>0.67434210526315697</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="11">
         <v>0.35121851320909198</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="11">
         <v>0.35397316821465402</v>
       </c>
     </row>
@@ -1322,22 +1329,22 @@
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="11">
         <v>0.61635944700460799</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="11">
         <v>0.93859649122806998</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="11">
         <v>0.74408901251738502</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="11">
         <v>0.68693384227478904</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="11">
         <v>0.41049259110933101</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="11">
         <v>0.46715852866673502</v>
       </c>
     </row>
@@ -1345,22 +1352,22 @@
       <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="10">
         <v>0.71022727272727204</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="11">
         <v>0.87719298245613997</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="10">
         <v>0.78492935635792704</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="10">
         <v>0.77415725158138105</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="10">
         <v>0.55374592833876202</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="10">
         <v>0.56742373669921198</v>
       </c>
     </row>
@@ -1368,22 +1375,22 @@
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="11">
         <v>0.60978835978835899</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="11">
         <v>0.80877192982456103</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="11">
         <v>0.69532428355957698</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="11">
         <v>0.66502199711432697</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="11">
         <v>0.34548400162008902</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="11">
         <v>0.362325682285638</v>
       </c>
     </row>
@@ -1391,88 +1398,85 @@
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="11">
         <v>0.58869701726844503</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="11">
         <v>0.65789473684210498</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="11">
         <v>0.62137531068765495</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="11">
         <v>0.62415704309892905</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="11">
         <v>0.25058932048785398</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="11">
         <v>0.25211563258686998</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="4">
-        <f>MAX(B22:B36)</f>
+      <c r="B37" s="12">
+        <f t="shared" ref="B37:G37" si="1">MAX(B22:B36)</f>
         <v>0.71022727272727204</v>
       </c>
-      <c r="C37" s="4">
-        <f>MAX(C22:C36)</f>
+      <c r="C37" s="12">
+        <f t="shared" si="1"/>
         <v>0.95087719298245599</v>
       </c>
-      <c r="D37" s="4">
-        <f>MAX(D22:D36)</f>
+      <c r="D37" s="12">
+        <f t="shared" si="1"/>
         <v>0.78492935635792704</v>
       </c>
-      <c r="E37" s="4">
-        <f>MAX(E22:E36)</f>
+      <c r="E37" s="12">
+        <f t="shared" si="1"/>
         <v>0.77415725158138105</v>
       </c>
-      <c r="F37" s="4">
-        <f>MAX(F22:F36)</f>
+      <c r="F37" s="12">
+        <f t="shared" si="1"/>
         <v>0.55374592833876202</v>
       </c>
-      <c r="G37" s="4">
-        <f>MAX(G22:G36)</f>
+      <c r="G37" s="12">
+        <f t="shared" si="1"/>
         <v>0.56742373669921198</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E38" s="3"/>
-    </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1480,22 +1484,22 @@
       <c r="A41" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="11">
         <v>0.83955223880596996</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="11">
         <v>0.84586466165413499</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="11">
         <v>0.84269662921348298</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="11">
         <v>0.76954108569107804</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="11">
         <v>0.53909465020576097</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="11">
         <v>0.53912711399211499</v>
       </c>
     </row>
@@ -1503,22 +1507,22 @@
       <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="11">
         <v>0.84379001280409704</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="11">
         <v>0.825814536340852</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="11">
         <v>0.83470550981633895</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="11">
         <v>0.76436330590465196</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="11">
         <v>0.52882771070743495</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="11">
         <v>0.52907692183310895</v>
       </c>
     </row>
@@ -1526,22 +1530,22 @@
       <c r="A43" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="11">
         <v>0.84840425531914898</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="11">
         <v>0.79949874686716704</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="11">
         <v>0.82322580645161203</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="11">
         <v>0.75628410503986498</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="11">
         <v>0.51332149200710397</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="11">
         <v>0.51504351692912198</v>
       </c>
     </row>
@@ -1549,22 +1553,22 @@
       <c r="A44" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="11">
         <v>0.84659746251441703</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="10">
         <v>0.91979949874686695</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="10">
         <v>0.88168168168168104</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="10">
         <v>0.81241841580824603</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="10">
         <v>0.62623028578204598</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="10">
         <v>0.63166660229242799</v>
       </c>
     </row>
@@ -1572,22 +1576,22 @@
       <c r="A45" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="11">
         <v>0.80253623188405798</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="11">
         <v>0.55513784461152804</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="11">
         <v>0.65629629629629604</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="11">
         <v>0.61373040323132699</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="11">
         <v>0.258193445243804</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="11">
         <v>0.28082317217761799</v>
       </c>
     </row>
@@ -1595,22 +1599,22 @@
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="11">
         <v>0.82078853046594902</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="11">
         <v>0.57393483709273097</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="11">
         <v>0.67551622418878998</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="11">
         <v>0.63329714555164396</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="11">
         <v>0.29444778512727998</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="11">
         <v>0.319018416662191</v>
       </c>
     </row>
@@ -1618,22 +1622,22 @@
       <c r="A47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="11">
         <v>0.85258358662613898</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="11">
         <v>0.70300751879699197</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="11">
         <v>0.77060439560439498</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="11">
         <v>0.71419564042514805</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="11">
         <v>0.43616796792572199</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="11">
         <v>0.44888432079016299</v>
       </c>
     </row>
@@ -1641,22 +1645,22 @@
       <c r="A48" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="11">
         <v>0.84910179640718497</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="11">
         <v>0.88847117794486197</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="11">
         <v>0.86834047764849898</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="11">
         <v>0.79962705985053195</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="11">
         <v>0.59967415338065799</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="11">
         <v>0.60110235151715796</v>
       </c>
     </row>
@@ -1664,22 +1668,22 @@
       <c r="A49" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="11">
         <v>0.86445783132530096</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="11">
         <v>0.71929824561403499</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="11">
         <v>0.78522571819425402</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="11">
         <v>0.73075718899403397</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="11">
         <v>0.46824724809483398</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="11">
         <v>0.48079013688613897</v>
       </c>
     </row>
@@ -1687,22 +1691,22 @@
       <c r="A50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="11">
         <v>0.87179487179487103</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="11">
         <v>0.68170426065162903</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="11">
         <v>0.76511954992967601</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="11">
         <v>0.71721324031137201</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="11">
         <v>0.44610281923714701</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="11">
         <v>0.465921900197036</v>
       </c>
     </row>
@@ -1710,22 +1714,22 @@
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="11">
         <v>0.86222910216718196</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="11">
         <v>0.69799498746867095</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="11">
         <v>0.77146814404432096</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="11">
         <v>0.71873002343916403</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="11">
         <v>0.44642482700775798</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="11">
         <v>0.46168522923260102</v>
       </c>
     </row>
@@ -1733,22 +1737,22 @@
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="11">
         <v>0.83986175115207296</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="11">
         <v>0.91353383458646598</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="13">
         <v>0.87515006002400897</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="11">
         <v>0.80180479502505897</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="11">
         <v>0.60512577123872802</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="11">
         <v>0.61054081430601603</v>
       </c>
     </row>
@@ -1756,22 +1760,22 @@
       <c r="A53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="10">
         <v>0.88636363636363602</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="11">
         <v>0.78195488721804496</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="11">
         <v>0.83089214380825505</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="11">
         <v>0.77888693211918103</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="11">
         <v>0.56055363321799301</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="11">
         <v>0.56811687940588296</v>
       </c>
     </row>
@@ -1779,22 +1783,22 @@
       <c r="A54" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="11">
         <v>0.83994708994709</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="11">
         <v>0.79573934837092697</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="11">
         <v>0.81724581724581702</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="11">
         <v>0.74689170133361404</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="11">
         <v>0.49443702714730697</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="11">
         <v>0.49582480155187098</v>
       </c>
     </row>
@@ -1802,51 +1806,51 @@
       <c r="A55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="11">
         <v>0.81789638932496</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="11">
         <v>0.65288220551378395</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="11">
         <v>0.72613240418118397</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="11">
         <v>0.66597492826912696</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="11">
         <v>0.34383804654074901</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="11">
         <v>0.35697716069371999</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="4">
-        <f>MAX(B41:B55)</f>
+      <c r="B56" s="12">
+        <f t="shared" ref="B56:G56" si="2">MAX(B41:B55)</f>
         <v>0.88636363636363602</v>
       </c>
-      <c r="C56" s="4">
-        <f>MAX(C41:C55)</f>
+      <c r="C56" s="12">
+        <f t="shared" si="2"/>
         <v>0.91979949874686695</v>
       </c>
-      <c r="D56" s="4">
-        <f>MAX(D41:D55)</f>
+      <c r="D56" s="12">
+        <f t="shared" si="2"/>
         <v>0.88168168168168104</v>
       </c>
-      <c r="E56" s="4">
-        <f>MAX(E41:E55)</f>
+      <c r="E56" s="12">
+        <f t="shared" si="2"/>
         <v>0.81241841580824603</v>
       </c>
-      <c r="F56" s="4">
-        <f>MAX(F41:F55)</f>
+      <c r="F56" s="12">
+        <f t="shared" si="2"/>
         <v>0.62623028578204598</v>
       </c>
-      <c r="G56" s="4">
-        <f>MAX(G41:G55)</f>
+      <c r="G56" s="12">
+        <f t="shared" si="2"/>
         <v>0.63166660229242799</v>
       </c>
     </row>
@@ -1903,83 +1907,83 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="3" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="3"/>
-    <col min="10" max="10" width="18.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="19" style="3" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="15" style="3" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="11" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="11" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="11"/>
+    <col min="10" max="10" width="18.7109375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" style="11" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" style="11" customWidth="1"/>
+    <col min="13" max="13" width="19" style="11" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" style="11" customWidth="1"/>
+    <col min="15" max="15" width="15" style="11" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="J1" s="7" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="J1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1987,43 +1991,43 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="11">
         <v>0.85</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="11">
         <v>0.64150943396226401</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="11">
         <v>0.50844854070660495</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="11">
         <v>0.73118279569892397</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="11">
         <v>6.5420560747663503E-2</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="11">
         <v>7.4854537802440002E-2</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="11">
         <v>0.82499999999999996</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="11">
         <v>0.63461538461538403</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="11">
         <v>0.49758454106280098</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="11">
         <v>0.71739130434782605</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="11">
         <v>3.7037037037037E-2</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="11">
         <v>4.13449115297361E-2</v>
       </c>
     </row>
@@ -2031,43 +2035,43 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="11">
         <v>0.31578947368421001</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="11">
         <v>0.66666666666666596</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="11">
         <v>0.63428571428571401</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="11">
         <v>0.42857142857142799</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="11">
         <v>0.29379310344827497</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="11">
         <v>0.32741151289660803</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="11">
         <v>0.84210526315789402</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="11">
         <v>0.69565217391304301</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="11">
         <v>0.82281284606866001</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="11">
         <v>0.76190476190476097</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="11">
         <v>0.64718853362734197</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="11">
         <v>0.653731177269543</v>
       </c>
     </row>
@@ -2075,43 +2079,43 @@
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="11">
         <v>0.86666666666666603</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="11">
         <v>0.72222222222222199</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="11">
         <v>0.85709728867623602</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="11">
         <v>0.78787878787878696</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="11">
         <v>0.71501272264630999</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="11">
         <v>0.72040625942068803</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="11">
         <v>1</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="11">
         <v>0.31914893617021201</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="11">
         <v>0.49951124144672499</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="11">
         <v>0.483870967741935</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="11">
         <v>0.199374511336982</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="11">
         <v>0.33275387468860201</v>
       </c>
     </row>
@@ -2119,43 +2123,43 @@
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="11">
         <v>0.78947368421052599</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="11">
         <v>0.73170731707317005</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="11">
         <v>0.68586928442262896</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="11">
         <v>0.759493670886076</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="11">
         <v>0.37319587628865902</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="11">
         <v>0.37503711732936901</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="11">
         <v>0.76315789473684204</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="11">
         <v>0.61702127659574402</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="11">
         <v>0.52722298221614206</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="11">
         <v>0.68235294117647005</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="11">
         <v>7.4946466809421797E-2</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="11">
         <v>7.8785478688117E-2</v>
       </c>
     </row>
@@ -2163,43 +2167,43 @@
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="11">
         <v>0.92307692307692302</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="11">
         <v>0.42857142857142799</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="11">
         <v>0.69498177740398004</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="11">
         <v>0.585365853658536</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="11">
         <v>0.42616033755274202</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="11">
         <v>0.49419043434758603</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="11">
         <v>0.84615384615384603</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="11">
         <v>0.5</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="11">
         <v>0.74439324116743399</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="11">
         <v>0.628571428571428</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="11">
         <v>0.50119904076738597</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="11">
         <v>0.53405198296199397</v>
       </c>
     </row>
@@ -2207,43 +2211,43 @@
       <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="11">
         <v>0.90196078431372495</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="11">
         <v>0.90196078431372495</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="11">
         <v>0.75867269984916996</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="11">
         <v>0.90196078431372495</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="11">
         <v>0.51734539969834004</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="11">
         <v>0.51734539969834004</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="11">
         <v>0.98039215686274495</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="11">
         <v>0.87719298245613997</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="11">
         <v>0.76296296296296295</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="11">
         <v>0.92592592592592504</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="11">
         <v>0.53369763205828702</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="11">
         <v>0.56967138923080396</v>
       </c>
     </row>
@@ -2251,43 +2255,43 @@
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="11">
         <v>0.62745098039215597</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="11">
         <v>0.67443105756358701</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="11">
         <v>0.77108433734939696</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="11">
         <v>0.40625</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="11">
         <v>0.50487816429740096</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="11">
         <v>0.8125</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="11">
         <v>0.63414634146341398</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="11">
         <v>0.66525529265255201</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="11">
         <v>0.71232876712328697</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="11">
         <v>0.34375</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="11">
         <v>0.35820928496420901</v>
       </c>
     </row>
@@ -2295,43 +2299,43 @@
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="11">
         <v>0.98039215686274495</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="11">
         <v>0.96153846153846101</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="11">
         <v>0.925436893203883</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="11">
         <v>0.970873786407767</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="11">
         <v>0.85093167701863304</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="11">
         <v>0.85198411871737401</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="11">
         <v>0.54901960784313697</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="11">
         <v>0.93333333333333302</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="11">
         <v>0.57972156553716803</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="11">
         <v>0.69135802469135799</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="11">
         <v>0.24670433145009399</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="11">
         <v>0.31859902414090802</v>
       </c>
     </row>
@@ -2339,43 +2343,43 @@
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="11">
         <v>0.72549019607843102</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="11">
         <v>0.97368421052631504</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="11">
         <v>0.72342264477095897</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="11">
         <v>0.83146067415730296</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="11">
         <v>0.47252747252747201</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="11">
         <v>0.53129192974498296</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="11">
         <v>0.86274509803921495</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="11">
         <v>0.88</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="11">
         <v>0.694902823615694</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="11">
         <v>0.87128712871287095</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="11">
         <v>0.39002932551319602</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="11">
         <v>0.39045937288056798</v>
       </c>
     </row>
@@ -2383,43 +2387,43 @@
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="11">
         <v>1</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="11">
         <v>0.95918367346938704</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="11">
         <v>0.95833333333333304</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="11">
         <v>0.97916666666666596</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="11">
         <v>0.91677503250975201</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="11">
         <v>0.91996659472731102</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="11">
         <v>0.97872340425531901</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="11">
         <v>0.95833333333333304</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="11">
         <v>0.93875598086124401</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="11">
         <v>0.96842105263157896</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="11">
         <v>0.87755102040816302</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="11">
         <v>0.87828292297109101</v>
       </c>
     </row>
@@ -2427,43 +2431,43 @@
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="11">
         <v>0.96</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="11">
         <v>0.94117647058823495</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="11">
         <v>0.882654932159882</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="11">
         <v>0.95049504950495001</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="11">
         <v>0.76539589442815203</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="11">
         <v>0.76623982196863305</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="11">
         <v>0.96</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="11">
         <v>0.94117647058823495</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="11">
         <v>0.882654932159882</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="11">
         <v>0.95049504950495001</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="11">
         <v>0.76539589442815203</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="11">
         <v>0.76623982196863305</v>
       </c>
     </row>
@@ -2471,43 +2475,43 @@
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="11">
         <v>0.6</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="11">
         <v>0.55555555555555503</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="11">
         <v>0.64372469635627505</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="11">
         <v>0.57692307692307598</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="11">
         <v>0.28816986855409499</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="11">
         <v>0.28877514330545001</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="11">
         <v>0.96</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="11">
         <v>0.42857142857142799</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="11">
         <v>0.44523246650906201</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="11">
         <v>0.592592592592592</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="11">
         <v>0.114093959731543</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="11">
         <v>0.205777361107392</v>
       </c>
     </row>
@@ -2515,43 +2519,43 @@
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="11">
         <v>1</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="11">
         <v>1</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="11">
         <v>1</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="11">
         <v>1</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="11">
         <v>1</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="11">
         <v>0.98245614035087703</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="11">
         <v>1</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="11">
         <v>0.96224188790560405</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="11">
         <v>0.99115044247787598</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="11">
         <v>0.92452830188679203</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="11">
         <v>0.92717264994552995</v>
       </c>
     </row>
@@ -2559,43 +2563,43 @@
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="11">
         <v>1</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="11">
         <v>0.92727272727272703</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="11">
         <v>0.89022298456260696</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="11">
         <v>0.96226415094339601</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="11">
         <v>0.78194207836456497</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="11">
         <v>0.80122284163523505</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="11">
         <v>0.98039215686274495</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="11">
         <v>0.90909090909090895</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="11">
         <v>0.83533447684391005</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="11">
         <v>0.94339622641509402</v>
       </c>
-      <c r="O16" s="3">
+      <c r="O16" s="11">
         <v>0.67291311754684802</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="11">
         <v>0.68950549552487606</v>
       </c>
     </row>
@@ -2603,43 +2607,43 @@
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="11">
         <v>0.92857142857142805</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="11">
         <v>0.98113207547169801</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="11">
         <v>0.84548527281506503</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="11">
         <v>0.95412844036697197</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="11">
         <v>0.69230769230769196</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="11">
         <v>0.70441600726860998</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="11">
         <v>0.83928571428571397</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="11">
         <v>0.97916666666666596</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="11">
         <v>0.74358974358974295</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="11">
         <v>0.90384615384615297</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="11">
         <v>0.5</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="11">
         <v>0.54554472558998102</v>
       </c>
     </row>
@@ -2647,43 +2651,43 @@
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="11">
         <v>0.77358490566037696</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="11">
         <v>0.95348837209302295</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="11">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="11">
         <v>0.85416666666666596</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="11">
         <v>0.43505674653215598</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="11">
         <v>0.47548951255627597</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="11">
         <v>1</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="11">
         <v>0.89830508474576198</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="11">
         <v>0.78571428571428503</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="11">
         <v>0.94642857142857095</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="11">
         <v>0.57986870897155296</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="11">
         <v>0.63899960333810502</v>
       </c>
     </row>
@@ -2691,43 +2695,43 @@
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="11">
         <v>0.9375</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="11">
         <v>0.83333333333333304</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="11">
         <v>0.91989987484355396</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="11">
         <v>0.88235294117647001</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="11">
         <v>0.84</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="11">
         <v>0.84270097160038404</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="11">
         <v>0.9375</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="11">
         <v>0.78947368421052599</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="11">
         <v>0.90168970814132099</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="11">
         <v>0.85714285714285698</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O19" s="11">
         <v>0.80392156862745101</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="11">
         <v>0.80954346627075902</v>
       </c>
     </row>
@@ -2735,43 +2739,43 @@
       <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="11">
         <v>0.78260869565217395</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="11">
         <v>1</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="11">
         <v>0.91028875805999399</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="11">
         <v>0.87804878048780399</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="11">
         <v>0.82182628062360796</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="11">
         <v>0.83519011792602305</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="11">
         <v>0.82608695652173902</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="11">
         <v>1</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="11">
         <v>0.92912513842746403</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="11">
         <v>0.90476190476190399</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="11">
         <v>0.85887541345093699</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="11">
         <v>0.86755807000506702</v>
       </c>
     </row>
@@ -2779,43 +2783,43 @@
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="11">
         <v>0.875</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="11">
         <v>0.875</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="11">
         <v>0.91666666666666596</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="11">
         <v>0.875</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="11">
         <v>0.83333333333333304</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="11">
         <v>0.83333333333333304</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="11">
         <v>0.875</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="11">
         <v>0.77777777777777701</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="11">
         <v>0.87984981226533099</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="11">
         <v>0.82352941176470495</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="11">
         <v>0.76</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="11">
         <v>0.76244373620987105</v>
       </c>
     </row>
@@ -2823,77 +2827,77 @@
       <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="11">
         <v>0.85316394288301001</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="11">
         <v>0.82533966910791401</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="11">
         <v>0.796750302790183</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="11">
         <v>0.82528515219252296</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="11">
         <v>0.60502337245165505</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="11">
         <v>0.624459674661897</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="11">
         <v>0.88529043363526705</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="11">
         <v>0.77752662018589003</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="11">
         <v>0.74202925942884101</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="11">
         <v>0.80825029014537597</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="11">
         <v>0.51742499282374599</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="11">
         <v>0.54571970259398905</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2901,22 +2905,22 @@
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="11">
         <v>0.72499999999999998</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="11">
         <v>0.707317073170731</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="11">
         <v>0.61334384029419398</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="11">
         <v>0.71604938271604901</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="11">
         <v>0.22689075630252001</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="11">
         <v>0.22701904283835</v>
       </c>
     </row>
@@ -2924,22 +2928,22 @@
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="11">
         <v>0.78947368421052599</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="11">
         <v>0.65217391304347805</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="11">
         <v>0.78737541528239197</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="11">
         <v>0.71428571428571397</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="11">
         <v>0.57662624035281096</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="11">
         <v>0.58245554635770203</v>
       </c>
     </row>
@@ -2947,22 +2951,22 @@
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="11">
         <v>0.53333333333333299</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="11">
         <v>0.42105263157894701</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="11">
         <v>0.63954943679599496</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="11">
         <v>0.47058823529411697</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="11">
         <v>0.28268991282689898</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="11">
         <v>0.28635128100358498</v>
       </c>
     </row>
@@ -2970,22 +2974,22 @@
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="11">
         <v>0.21052631578947301</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="11">
         <v>0.72727272727272696</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="11">
         <v>0.45440454662877799</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="11">
         <v>0.32653061224489699</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="11">
         <v>8.1739130434782606E-2</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="11">
         <v>0.12385544497037899</v>
       </c>
     </row>
@@ -2993,22 +2997,22 @@
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="11">
         <v>0.92307692307692302</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="11">
         <v>0.63157894736842102</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="11">
         <v>0.83333333333333304</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="11">
         <v>0.75</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="11">
         <v>0.67052767052767004</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="11">
         <v>0.69198694592824295</v>
       </c>
     </row>
@@ -3016,22 +3020,22 @@
       <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="11">
         <v>0.58823529411764697</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="11">
         <v>0.967741935483871</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="11">
         <v>0.62672322375397604</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="11">
         <v>0.73170731707317005</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="11">
         <v>0.32502396931927102</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="11">
         <v>0.411628197349662</v>
       </c>
     </row>
@@ -3039,22 +3043,22 @@
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="11">
         <v>0.5</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="11">
         <v>0.61538461538461497</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="11">
         <v>0.59014778325123096</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="11">
         <v>0.55172413793103403</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="11">
         <v>0.1875</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="11">
         <v>0.19088542889273299</v>
       </c>
     </row>
@@ -3062,22 +3066,22 @@
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="11">
         <v>0.68627450980392102</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="11">
         <v>1</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="11">
         <v>0.71650055370985599</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="11">
         <v>0.81395348837209303</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="11">
         <v>0.47052740434332901</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="11">
         <v>0.55465331288860897</v>
       </c>
     </row>
@@ -3085,22 +3089,22 @@
       <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="11">
         <v>0.50980392156862697</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="11">
         <v>1</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="11">
         <v>0.59256429844665104</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="11">
         <v>0.67532467532467499</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="11">
         <v>0.29701230228470998</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="11">
         <v>0.417620168032103</v>
       </c>
     </row>
@@ -3108,22 +3112,22 @@
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="11">
         <v>1</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="11">
         <v>0.95918367346938704</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="11">
         <v>0.95833333333333304</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="11">
         <v>0.97916666666666596</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="11">
         <v>0.91677503250975201</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="11">
         <v>0.91996659472731102</v>
       </c>
     </row>
@@ -3131,22 +3135,22 @@
       <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="11">
         <v>0.96</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="11">
         <v>0.94117647058823495</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="11">
         <v>0.882654932159882</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="11">
         <v>0.95049504950495001</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="11">
         <v>0.76539589442815203</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="11">
         <v>0.76623982196863305</v>
       </c>
     </row>
@@ -3154,22 +3158,22 @@
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="11">
         <v>0.24</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="11">
         <v>0.75</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="11">
         <v>0.57129186602870796</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="11">
         <v>0.36363636363636298</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="11">
         <v>0.21495327102803699</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="11">
         <v>0.27840466502764899</v>
       </c>
     </row>
@@ -3177,22 +3181,22 @@
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="11">
         <v>0.94736842105263097</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="11">
         <v>1</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="11">
         <v>0.89825119236883899</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="11">
         <v>0.97297297297297303</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="11">
         <v>0.797468354430379</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="11">
         <v>0.81434507104595499</v>
       </c>
     </row>
@@ -3200,22 +3204,22 @@
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="11">
         <v>1</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="11">
         <v>0.91071428571428503</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="11">
         <v>0.85758789497107202</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="11">
         <v>0.95327102803738295</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="11">
         <v>0.71830985915492895</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="11">
         <v>0.74862511341763005</v>
       </c>
     </row>
@@ -3223,22 +3227,22 @@
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="11">
         <v>0.73214285714285698</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="11">
         <v>1</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="11">
         <v>0.68074492850016599</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="11">
         <v>0.84536082474226804</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="11">
         <v>0.40594059405940502</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="11">
         <v>0.50463688439626297</v>
       </c>
     </row>
@@ -3246,22 +3250,22 @@
       <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="11">
         <v>0.64150943396226401</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="11">
         <v>0.94444444444444398</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="11">
         <v>0.61279170267934302</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="11">
         <v>0.76404494382022403</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="11">
         <v>0.28510638297872298</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="11">
         <v>0.34959905545923597</v>
       </c>
     </row>
@@ -3269,22 +3273,22 @@
       <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="11">
         <v>0.8125</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="11">
         <v>0.92857142857142805</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="11">
         <v>0.91292517006802698</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="11">
         <v>0.86666666666666603</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="11">
         <v>0.82608695652173902</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="11">
         <v>0.82922798289677102</v>
       </c>
     </row>
@@ -3292,22 +3296,22 @@
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="11">
         <v>0.82608695652173902</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="11">
         <v>0.95</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="11">
         <v>0.91244870041039605</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="11">
         <v>0.88372093023255804</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="11">
         <v>0.82532751091703005</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="11">
         <v>0.82989779952672904</v>
       </c>
     </row>
@@ -3315,22 +3319,22 @@
       <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="11">
         <v>0.5</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="11">
         <v>0.8</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="11">
         <v>0.75867269984916996</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="11">
         <v>0.61538461538461497</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="11">
         <v>0.52380952380952295</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="11">
         <v>0.54659439449994796</v>
       </c>
     </row>
@@ -3338,22 +3342,22 @@
       <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="11">
         <v>0.69080692897789098</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="11">
         <v>0.83719011295213497</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="11">
         <v>0.73156025536133396</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="11">
         <v>0.73394124341612699</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="11">
         <v>0.494616356117351</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="11">
         <v>0.53021014480144701</v>
       </c>
     </row>
@@ -3385,83 +3389,86 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" style="11" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="11"/>
+    <col min="9" max="9" width="13.5703125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="11" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="11"/>
+    <col min="13" max="13" width="12.85546875" style="11" customWidth="1"/>
+    <col min="14" max="16" width="9.140625" style="11"/>
+    <col min="17" max="17" width="12.28515625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="G1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="K1" s="9" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="K1" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="O1" s="9" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="O1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="12" t="s">
         <v>50</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="12" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3469,45 +3476,45 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="11">
         <v>0.50844854070660495</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="11">
         <v>6.5420560747663503E-2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="11">
         <f>B3-H3</f>
         <v>-0.21120102124583506</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="11">
         <f>B3-P3</f>
         <v>-0.35904628330995803</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="15">
         <v>0.71964956195244001</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="15">
         <v>0.46347305389221499</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="15">
         <v>0.74439324116743399</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="15">
         <v>0.50710900473933596</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="5">
+      <c r="P3" s="15">
         <v>0.86749482401656297</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="Q3" s="15">
         <v>0.73509933774834402</v>
       </c>
     </row>
@@ -3515,45 +3522,45 @@
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="11">
         <v>0.63428571428571401</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="11">
         <v>0.29379310344827497</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="11">
         <f t="shared" ref="D4:D21" si="0">B4-H4</f>
         <v>9.2857142857140085E-3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="11">
         <f t="shared" ref="E4:E21" si="1">B4-P4</f>
         <v>5.0952380952380971E-2</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="15">
         <v>0.625</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="15">
         <v>0.294981640146878</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="15">
         <v>0.79639448568398696</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="15">
         <v>0.59278897136797404</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="15">
         <v>0.58333333333333304</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="15">
         <v>0.21664626682986499</v>
       </c>
     </row>
@@ -3561,45 +3568,45 @@
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="11">
         <v>0.85709728867623602</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="11">
         <v>0.71501272264630999</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="11">
         <f t="shared" si="0"/>
         <v>0.142217573796522</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="11">
         <f t="shared" si="1"/>
         <v>0.34159057316952102</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="15">
         <v>0.71487971487971402</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="15">
         <v>0.42992874109263601</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="15">
         <v>0.53079178885630496</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="15">
         <v>0.21246923707957299</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="15">
         <v>0.51550671550671501</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5" s="15">
         <v>0.19611021069692</v>
       </c>
     </row>
@@ -3607,45 +3614,45 @@
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="11">
         <v>0.68586928442262896</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="11">
         <v>0.37319587628865902</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="11">
         <f t="shared" si="0"/>
         <v>0.23647657187202198</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="11">
         <f t="shared" si="1"/>
         <v>-0.1686761701228251</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="15">
         <v>0.44939271255060698</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="15">
         <v>0.103050288540807</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="15">
         <v>0.36945812807881701</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="15">
         <v>4.4062733383121701E-2</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="5">
+      <c r="P6" s="15">
         <v>0.85454545454545405</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="15">
         <v>0.71203599550056196</v>
       </c>
     </row>
@@ -3653,45 +3660,45 @@
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="11">
         <v>0.69498177740398004</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="11">
         <v>0.42616033755274202</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="11">
         <f t="shared" si="0"/>
         <v>-0.15371798618939991</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="11">
         <f t="shared" si="1"/>
         <v>-0.17373617131396801</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="15">
         <v>0.84869976359337995</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="15">
         <v>0.70370370370370305</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="15">
         <v>0.91028875805999399</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="15">
         <v>0.82102908277404896</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="15">
         <v>0.86871794871794805</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="Q7" s="15">
         <v>0.73983739837398299</v>
       </c>
     </row>
@@ -3699,45 +3706,45 @@
       <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="11">
         <v>0.75867269984916996</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="11">
         <v>0.51734539969834004</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="11">
         <f t="shared" si="0"/>
         <v>0.13194947609519392</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="11">
         <f t="shared" si="1"/>
         <v>-6.3549522373052003E-2</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="15">
         <v>0.62672322375397604</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="15">
         <v>0.32502396931927102</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="15">
         <v>0.527272727272727</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="15">
         <v>0.20686367969494701</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8" s="15">
         <v>0.82222222222222197</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8" s="15">
         <v>0.65027322404371501</v>
       </c>
     </row>
@@ -3745,45 +3752,45 @@
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="11">
         <v>0.67443105756358701</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="11">
         <v>0.40625</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="11">
         <f t="shared" si="0"/>
         <v>0.17965132748974</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="11">
         <f t="shared" si="1"/>
         <v>-9.3684884465398022E-2</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="15">
         <v>0.49477973007384701</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="15">
         <v>0.12829525483304</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="15">
         <v>0.54587717151945103</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="15">
         <v>0.13914656771799599</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="15">
         <v>0.76811594202898503</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="15">
         <v>0.54982415005861596</v>
       </c>
     </row>
@@ -3791,45 +3798,45 @@
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="11">
         <v>0.925436893203883</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="11">
         <v>0.85093167701863304</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="11">
         <f t="shared" si="0"/>
         <v>0.23045511579990297</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="11">
         <f t="shared" si="1"/>
         <v>0.36658217422191097</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="15">
         <v>0.69498177740398004</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="15">
         <v>0.43568464730290402</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="15">
         <v>0.73431013431013403</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="15">
         <v>0.47184466019417398</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="15">
         <v>0.55885471898197203</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10" s="15">
         <v>0.21804511278195399</v>
       </c>
     </row>
@@ -3837,45 +3844,45 @@
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="11">
         <v>0.72342264477095897</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="11">
         <v>0.47252747252747201</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="11">
         <f t="shared" si="0"/>
         <v>6.7172644770958967E-2</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="11">
         <f t="shared" si="1"/>
         <v>5.0695372043687015E-2</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="15">
         <v>0.65625</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="15">
         <v>0.33584905660377301</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="15">
         <v>0.51417004048582904</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="15">
         <v>0.151943462897526</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="5">
+      <c r="P11" s="15">
         <v>0.67272727272727195</v>
       </c>
-      <c r="Q11" s="5">
+      <c r="Q11" s="15">
         <v>0.37117903930131002</v>
       </c>
     </row>
@@ -3883,45 +3890,45 @@
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="11">
         <v>0.95833333333333304</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="11">
         <v>0.91677503250975201</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="11">
         <f t="shared" si="0"/>
         <v>-4.1666666666666963E-2</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="11">
         <f t="shared" si="1"/>
         <v>-2.038299523334397E-2</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="15">
         <v>1</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="15">
         <v>1</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="15">
         <v>0.97871632856667701</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="15">
         <v>0.95744680851063801</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="P12" s="5">
+      <c r="P12" s="15">
         <v>0.97871632856667701</v>
       </c>
-      <c r="Q12" s="5">
+      <c r="Q12" s="15">
         <v>0.95744680851063801</v>
       </c>
     </row>
@@ -3929,45 +3936,45 @@
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="11">
         <v>0.882654932159882</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="11">
         <v>0.76539589442815203</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="11">
         <f t="shared" si="0"/>
         <v>-0.117345067840118</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="11">
         <f t="shared" si="1"/>
         <v>-0.117345067840118</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="15">
         <v>1</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="15">
         <v>1</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="15">
         <v>1</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="15">
         <v>1</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="5">
+      <c r="P13" s="15">
         <v>1</v>
       </c>
-      <c r="Q13" s="5">
+      <c r="Q13" s="15">
         <v>1</v>
       </c>
     </row>
@@ -3975,45 +3982,45 @@
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="11">
         <v>0.64372469635627505</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="11">
         <v>0.28816986855409499</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="11">
         <f t="shared" si="0"/>
         <v>9.5952038906199077E-2</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="11">
         <f t="shared" si="1"/>
         <v>0.14064571375922108</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="15">
         <v>0.54777265745007597</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="15">
         <v>0.185840707964601</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="15">
         <v>0.25</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="15">
         <v>0.04</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="P14" s="5">
+      <c r="P14" s="15">
         <v>0.50307898259705397</v>
       </c>
-      <c r="Q14" s="5">
+      <c r="Q14" s="15">
         <v>0.188811188811188</v>
       </c>
     </row>
@@ -4021,45 +4028,45 @@
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="11">
         <v>1</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="11">
         <v>1</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="11">
         <f t="shared" si="0"/>
         <v>0.10174880763116101</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="11">
         <f t="shared" si="1"/>
         <v>3.7758112094395946E-2</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="15">
         <v>0.89825119236883899</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="15">
         <v>0.797468354430379</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="15">
         <v>0.87070707070706999</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="15">
         <v>0.74193548387096697</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="P15" s="5">
+      <c r="P15" s="15">
         <v>0.96224188790560405</v>
       </c>
-      <c r="Q15" s="5">
+      <c r="Q15" s="15">
         <v>0.92452830188679203</v>
       </c>
     </row>
@@ -4067,45 +4074,45 @@
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="11">
         <v>0.89022298456260696</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="11">
         <v>0.78194207836456497</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="11">
         <f t="shared" si="0"/>
         <v>-7.5860746227006004E-2</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="11">
         <f t="shared" si="1"/>
         <v>-4.5130550790928092E-2</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="15">
         <v>0.96608373078961296</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="15">
         <v>0.93220338983050799</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="15">
         <v>0.96608373078961296</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="15">
         <v>0.93220338983050799</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="O16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P16" s="15">
         <v>0.93535353535353505</v>
       </c>
-      <c r="Q16" s="5">
+      <c r="Q16" s="15">
         <v>0.87070707070706999</v>
       </c>
     </row>
@@ -4113,45 +4120,45 @@
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="11">
         <v>0.84548527281506503</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="11">
         <v>0.69230769230769196</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="11">
         <f t="shared" si="0"/>
         <v>0.16588577344084798</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="11">
         <f t="shared" si="1"/>
         <v>0.10364442206332403</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="15">
         <v>0.67959949937421704</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="15">
         <v>0.38682634730538901</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="15">
         <v>0.76029962546816399</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="15">
         <v>0.527272727272727</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="O17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="P17" s="5">
+      <c r="P17" s="15">
         <v>0.741840850751741</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="Q17" s="15">
         <v>0.48837209302325502</v>
       </c>
     </row>
@@ -4159,45 +4166,45 @@
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="11">
         <v>0.70833333333333304</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="11">
         <v>0.43505674653215598</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="11">
         <f t="shared" si="0"/>
         <v>8.859683113751804E-2</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="11">
         <f t="shared" si="1"/>
         <v>9.4457013574661075E-2</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="15">
         <v>0.619736502195815</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="15">
         <v>0.24897959183673399</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="15">
         <v>0.53046251993620397</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="15">
         <v>0.19650655021833999</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="15">
         <v>0.61387631975867196</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q18" s="15">
         <v>0.29573590096286101</v>
       </c>
     </row>
@@ -4205,45 +4212,45 @@
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="11">
         <v>0.91989987484355396</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="11">
         <v>0.84</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="11">
         <f t="shared" si="0"/>
         <v>3.2332081768879917E-3</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="11">
         <f t="shared" si="1"/>
         <v>-2.3076068132389049E-2</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="15">
         <v>0.91666666666666596</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="15">
         <v>0.83419689119170903</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="15">
         <v>0.89792663476874002</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="15">
         <v>0.797468354430379</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="P19" s="5">
+      <c r="P19" s="15">
         <v>0.942975942975943</v>
       </c>
-      <c r="Q19" s="5">
+      <c r="Q19" s="15">
         <v>0.88598574821852705</v>
       </c>
     </row>
@@ -4251,45 +4258,45 @@
       <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="11">
         <v>0.91028875805999399</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="11">
         <v>0.82182628062360796</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="11">
         <f t="shared" si="0"/>
         <v>-5.2284341355209984E-2</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="11">
         <f t="shared" si="1"/>
         <v>-3.2687184915949019E-2</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="15">
         <v>0.96257309941520397</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="15">
         <v>0.92523364485981296</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="15">
         <v>0.94468452895419097</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="15">
         <v>0.88940092165898599</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="P20" s="5">
+      <c r="P20" s="15">
         <v>0.942975942975943</v>
       </c>
-      <c r="Q20" s="5">
+      <c r="Q20" s="15">
         <v>0.88598574821852705</v>
       </c>
     </row>
@@ -4297,73 +4304,70 @@
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="11">
         <v>0.91666666666666596</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="11">
         <v>0.83333333333333304</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="11">
         <f t="shared" si="0"/>
         <v>0.157993966817496</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="11">
         <f t="shared" si="1"/>
         <v>-3.2332081768879917E-3</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="15">
         <v>0.75867269984916996</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="15">
         <v>0.52380952380952295</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="15">
         <v>0.72571428571428498</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="15">
         <v>0.463687150837988</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="P21" s="5">
+      <c r="P21" s="15">
         <v>0.91989987484355396</v>
       </c>
-      <c r="Q21" s="5">
+      <c r="Q21" s="15">
         <v>0.84</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C22" s="3"/>
-    </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="12" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4371,17 +4375,17 @@
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="11">
         <v>0.61334384029419398</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="11">
         <v>0.22689075630252001</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="11">
         <f>B25-H3</f>
         <v>-0.10630572165824603</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="11">
         <f>B25-L3</f>
         <v>-0.13104940087324002</v>
       </c>
@@ -4390,17 +4394,17 @@
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="11">
         <v>0.78737541528239197</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="11">
         <v>0.57662624035281096</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="11">
         <f t="shared" ref="D26:D43" si="2">B26-H4</f>
         <v>0.16237541528239197</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="11">
         <f t="shared" ref="E26:E43" si="3">B26-L4</f>
         <v>-9.0190704015949974E-3</v>
       </c>
@@ -4409,17 +4413,17 @@
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="11">
         <v>0.63954943679599496</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="11">
         <v>0.28268991282689898</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="11">
         <f t="shared" si="2"/>
         <v>-7.533027808371906E-2</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="11">
         <f t="shared" si="3"/>
         <v>0.10875764793969001</v>
       </c>
@@ -4428,17 +4432,17 @@
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="11">
         <v>0.45440454662877799</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="11">
         <v>8.1739130434782606E-2</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="11">
         <f t="shared" si="2"/>
         <v>5.011834078171018E-3</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="11">
         <f t="shared" si="3"/>
         <v>8.4946418549960989E-2</v>
       </c>
@@ -4447,17 +4451,17 @@
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="11">
         <v>0.83333333333333304</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="11">
         <v>0.67052767052767004</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="11">
         <f t="shared" si="2"/>
         <v>-1.5366430260046915E-2</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="11">
         <f t="shared" si="3"/>
         <v>-7.6955424726660948E-2</v>
       </c>
@@ -4466,17 +4470,17 @@
       <c r="A30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="11">
         <v>0.62672322375397604</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="11">
         <v>0.32502396931927102</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="11">
         <f t="shared" si="3"/>
         <v>9.945049648124904E-2</v>
       </c>
@@ -4485,17 +4489,17 @@
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="11">
         <v>0.59014778325123096</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="11">
         <v>0.1875</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="11">
         <f t="shared" si="2"/>
         <v>9.5368053177383949E-2</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="11">
         <f t="shared" si="3"/>
         <v>4.427061173177993E-2</v>
       </c>
@@ -4504,17 +4508,17 @@
       <c r="A32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="11">
         <v>0.71650055370985599</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="11">
         <v>0.47052740434332901</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="11">
         <f t="shared" si="2"/>
         <v>2.1518776305875953E-2</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="11">
         <f t="shared" si="3"/>
         <v>-1.7809580600278041E-2</v>
       </c>
@@ -4523,17 +4527,17 @@
       <c r="A33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="11">
         <v>0.59256429844665104</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="11">
         <v>0.29701230228470998</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="11">
         <f t="shared" si="2"/>
         <v>-6.3685701553348961E-2</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="11">
         <f t="shared" si="3"/>
         <v>7.8394257960822E-2</v>
       </c>
@@ -4542,17 +4546,17 @@
       <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="11">
         <v>0.95833333333333304</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="11">
         <v>0.91677503250975201</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="11">
         <f t="shared" si="2"/>
         <v>-4.1666666666666963E-2</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="11">
         <f t="shared" si="3"/>
         <v>-2.038299523334397E-2</v>
       </c>
@@ -4561,17 +4565,17 @@
       <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="11">
         <v>0.882654932159882</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="11">
         <v>0.76539589442815203</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="11">
         <f t="shared" si="2"/>
         <v>-0.117345067840118</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="11">
         <f t="shared" si="3"/>
         <v>-0.117345067840118</v>
       </c>
@@ -4580,17 +4584,17 @@
       <c r="A36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="11">
         <v>0.57129186602870796</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="11">
         <v>0.21495327102803699</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="11">
         <f t="shared" si="2"/>
         <v>2.3519208578631989E-2</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="11">
         <f t="shared" si="3"/>
         <v>0.32129186602870796</v>
       </c>
@@ -4599,17 +4603,17 @@
       <c r="A37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="11">
         <v>0.89825119236883899</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="11">
         <v>0.797468354430379</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="11">
         <f t="shared" si="3"/>
         <v>2.7544121661769005E-2</v>
       </c>
@@ -4618,17 +4622,17 @@
       <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="11">
         <v>0.85758789497107202</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="11">
         <v>0.71830985915492895</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="11">
         <f t="shared" si="2"/>
         <v>-0.10849583581854094</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="11">
         <f t="shared" si="3"/>
         <v>-0.10849583581854094</v>
       </c>
@@ -4637,17 +4641,17 @@
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="11">
         <v>0.68074492850016599</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="11">
         <v>0.40594059405940502</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="11">
         <f t="shared" si="2"/>
         <v>1.1454291259489491E-3</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="11">
         <f t="shared" si="3"/>
         <v>-7.9554696967997995E-2</v>
       </c>
@@ -4656,17 +4660,17 @@
       <c r="A40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="11">
         <v>0.61279170267934302</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="11">
         <v>0.28510638297872298</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="11">
         <f t="shared" si="2"/>
         <v>-6.9447995164719778E-3</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="11">
         <f t="shared" si="3"/>
         <v>8.2329182743139051E-2</v>
       </c>
@@ -4675,17 +4679,17 @@
       <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="11">
         <v>0.91292517006802698</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="11">
         <v>0.82608695652173902</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="11">
         <f t="shared" si="2"/>
         <v>-3.7414965986389825E-3</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="11">
         <f t="shared" si="3"/>
         <v>1.4998535299286964E-2</v>
       </c>
@@ -4694,17 +4698,17 @@
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="11">
         <v>0.91244870041039605</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="11">
         <v>0.82532751091703005</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="11">
         <f t="shared" si="2"/>
         <v>-5.0124399004807918E-2</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="11">
         <f t="shared" si="3"/>
         <v>-3.223582854379492E-2</v>
       </c>
@@ -4713,46 +4717,43 @@
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="11">
         <v>0.75867269984916996</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="11">
         <v>0.52380952380952295</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="11">
         <f t="shared" si="3"/>
         <v>3.2958414134884984E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="3"/>
-    </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="12" t="s">
         <v>49</v>
       </c>
     </row>
@@ -4760,17 +4761,17 @@
       <c r="A47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="11">
         <v>0.49758454106280098</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="11">
         <v>3.7037037037037E-2</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="11">
         <f>B47-P3</f>
         <v>-0.36991028295376199</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="11">
         <f>B47-L3</f>
         <v>-0.24680870010463302</v>
       </c>
@@ -4779,17 +4780,17 @@
       <c r="A48" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="11">
         <v>0.82281284606866001</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="11">
         <v>0.64718853362734197</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="11">
         <f t="shared" ref="D48:D65" si="4">B48-P4</f>
         <v>0.23947951273532697</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="11">
         <f t="shared" ref="E48:E65" si="5">B48-L4</f>
         <v>2.6418360384673045E-2</v>
       </c>
@@ -4798,17 +4799,17 @@
       <c r="A49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="11">
         <v>0.49951124144672499</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="11">
         <v>0.199374511336982</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="11">
         <f t="shared" si="4"/>
         <v>-1.5995474059990022E-2</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="11">
         <f t="shared" si="5"/>
         <v>-3.1280547409579973E-2</v>
       </c>
@@ -4817,17 +4818,17 @@
       <c r="A50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="11">
         <v>0.52722298221614206</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="11">
         <v>7.4946466809421797E-2</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="11">
         <f t="shared" si="4"/>
         <v>-0.327322472329312</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="11">
         <f t="shared" si="5"/>
         <v>0.15776485413732505</v>
       </c>
@@ -4836,17 +4837,17 @@
       <c r="A51" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="11">
         <v>0.74439324116743399</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="11">
         <v>0.50119904076738597</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="11">
         <f t="shared" si="4"/>
         <v>-0.12432470755051406</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="11">
         <f t="shared" si="5"/>
         <v>-0.16589551689255999</v>
       </c>
@@ -4855,17 +4856,17 @@
       <c r="A52" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="11">
         <v>0.76296296296296295</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="11">
         <v>0.53369763205828702</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="11">
         <f t="shared" si="4"/>
         <v>-5.9259259259259012E-2</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="11">
         <f t="shared" si="5"/>
         <v>0.23569023569023595</v>
       </c>
@@ -4874,17 +4875,17 @@
       <c r="A53" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="11">
         <v>0.66525529265255201</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="11">
         <v>0.34375</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="11">
         <f t="shared" si="4"/>
         <v>-0.10286064937643302</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="11">
         <f t="shared" si="5"/>
         <v>0.11937812113310098</v>
       </c>
@@ -4893,17 +4894,17 @@
       <c r="A54" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="11">
         <v>0.57972156553716803</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="11">
         <v>0.24670433145009399</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="11">
         <f t="shared" si="4"/>
         <v>2.0866846555195995E-2</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="11">
         <f t="shared" si="5"/>
         <v>-0.15458856877296601</v>
       </c>
@@ -4912,17 +4913,17 @@
       <c r="A55" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="11">
         <v>0.694902823615694</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="11">
         <v>0.39002932551319602</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="11">
         <f t="shared" si="4"/>
         <v>2.2175550888422046E-2</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="11">
         <f t="shared" si="5"/>
         <v>0.18073278312986496</v>
       </c>
@@ -4931,17 +4932,17 @@
       <c r="A56" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="11">
         <v>0.93875598086124401</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="11">
         <v>0.87755102040816302</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="11">
         <f t="shared" si="4"/>
         <v>-3.9960347705432997E-2</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="11">
         <f t="shared" si="5"/>
         <v>-3.9960347705432997E-2</v>
       </c>
@@ -4950,17 +4951,17 @@
       <c r="A57" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="11">
         <v>0.882654932159882</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="11">
         <v>0.76539589442815203</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="11">
         <f t="shared" si="4"/>
         <v>-0.117345067840118</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="11">
         <f t="shared" si="5"/>
         <v>-0.117345067840118</v>
       </c>
@@ -4969,17 +4970,17 @@
       <c r="A58" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="11">
         <v>0.44523246650906201</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="11">
         <v>0.114093959731543</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="11">
         <f t="shared" si="4"/>
         <v>-5.7846516087991962E-2</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="11">
         <f t="shared" si="5"/>
         <v>0.19523246650906201</v>
       </c>
@@ -4988,17 +4989,17 @@
       <c r="A59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="11">
         <v>0.96224188790560405</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="11">
         <v>0.92452830188679203</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="11">
         <f t="shared" si="5"/>
         <v>9.1534817198534069E-2</v>
       </c>
@@ -5007,17 +5008,17 @@
       <c r="A60" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="11">
         <v>0.83533447684391005</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="11">
         <v>0.67291311754684802</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="11">
         <f t="shared" si="4"/>
         <v>-0.100019058509625</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="11">
         <f t="shared" si="5"/>
         <v>-0.13074925394570291</v>
       </c>
@@ -5026,17 +5027,17 @@
       <c r="A61" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="11">
         <v>0.74358974358974295</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="11">
         <v>0.5</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="11">
         <f t="shared" si="4"/>
         <v>1.7488928380019475E-3</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="11">
         <f t="shared" si="5"/>
         <v>-1.670988187842104E-2</v>
       </c>
@@ -5045,17 +5046,17 @@
       <c r="A62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="11">
         <v>0.78571428571428503</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="11">
         <v>0.57986870897155296</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="11">
         <f t="shared" si="4"/>
         <v>0.17183796595561307</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="11">
         <f t="shared" si="5"/>
         <v>0.25525176577808106</v>
       </c>
@@ -5064,17 +5065,17 @@
       <c r="A63" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="11">
         <v>0.90168970814132099</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="11">
         <v>0.80392156862745101</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="11">
         <f t="shared" si="4"/>
         <v>-4.1286234834622015E-2</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="11">
         <f t="shared" si="5"/>
         <v>3.7630733725809717E-3</v>
       </c>
@@ -5083,17 +5084,17 @@
       <c r="A64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="11">
         <v>0.92912513842746403</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="11">
         <v>0.85887541345093699</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="11">
         <f t="shared" si="4"/>
         <v>-1.3850804548478979E-2</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="11">
         <f t="shared" si="5"/>
         <v>-1.5559390526726946E-2</v>
       </c>
@@ -5102,17 +5103,17 @@
       <c r="A65" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="11">
         <v>0.87984981226533099</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="11">
         <v>0.76</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="11">
         <f t="shared" si="4"/>
         <v>-4.0050062578222967E-2</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65" s="11">
         <f t="shared" si="5"/>
         <v>0.15413552655104601</v>
       </c>
@@ -5243,11 +5244,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:E2">
-    <cfRule type="colorScale" priority="27">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5263,11 +5264,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5275,11 +5276,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:E24">
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5295,11 +5296,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="26">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5473,11 +5474,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K21">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5493,11 +5494,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5537,11 +5538,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O21">
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5557,11 +5558,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>

--- a/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
+++ b/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\initial_testing_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB674386-461F-4967-8463-5E7CA77FD6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4620F94D-D1ED-43F7-A824-990DBC4A20B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="4" r:id="rId1"/>
@@ -289,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -299,28 +299,27 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -338,36 +337,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -657,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F8CBD-665F-4514-96E7-546603B512CB}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -666,19 +635,23 @@
     <col min="4" max="4" width="17.140625" style="5" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="14.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -698,7 +671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -717,8 +690,11 @@
       <c r="F3" s="7">
         <v>0.56790237588980297</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -737,8 +713,11 @@
       <c r="F4" s="7">
         <v>0.60442987182720698</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -757,8 +736,11 @@
       <c r="F5" s="7">
         <v>0.59625862695241505</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
@@ -777,8 +759,11 @@
       <c r="F6" s="7">
         <v>0.67138435366112903</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
@@ -797,8 +782,11 @@
       <c r="F7" s="7">
         <v>0.320677619817825</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
@@ -817,8 +805,11 @@
       <c r="F8" s="7">
         <v>0.35685204527529601</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
@@ -837,8 +828,11 @@
       <c r="F9" s="7">
         <v>0.45795544598045201</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -857,8 +851,11 @@
       <c r="F10" s="7">
         <v>0.59339298647290994</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
@@ -877,8 +874,11 @@
       <c r="F11" s="7">
         <v>0.53764768118497597</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
@@ -897,8 +897,11 @@
       <c r="F12" s="7">
         <v>0.57895655208515096</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
@@ -917,8 +920,11 @@
       <c r="F13" s="7">
         <v>0.60225374696568101</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
@@ -937,8 +943,11 @@
       <c r="F14" s="7">
         <v>0.58985040711986303</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
@@ -957,8 +966,11 @@
       <c r="F15" s="7">
         <v>0.67202557967935905</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
@@ -977,8 +989,11 @@
       <c r="F16" s="7">
         <v>0.363630338245365</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>15</v>
       </c>
@@ -997,8 +1012,11 @@
       <c r="F17" s="7">
         <v>0.57960726468147805</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>51</v>
       </c>
@@ -1017,8 +1035,11 @@
       <c r="F18" s="7">
         <v>0.67550826272592501</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>52</v>
       </c>
@@ -1037,8 +1058,11 @@
       <c r="F19" s="6">
         <v>0.73632332330032302</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>53</v>
       </c>
@@ -1057,9 +1081,12 @@
       <c r="F20" s="7">
         <v>0.48988982228038302</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="4">
@@ -1083,17 +1110,17 @@
         <v>0.73632332330032302</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>0</v>
       </c>
@@ -1113,7 +1140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>1</v>
       </c>
@@ -1133,7 +1160,7 @@
         <v>0.41636436920596498</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
@@ -1153,7 +1180,7 @@
         <v>0.41339258660741302</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -1173,7 +1200,7 @@
         <v>0.40356564019448898</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>4</v>
       </c>
@@ -1193,7 +1220,7 @@
         <v>0.43446480424551898</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>5</v>
       </c>
@@ -1213,7 +1240,7 @@
         <v>0.25919801570897</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>6</v>
       </c>
@@ -1233,7 +1260,7 @@
         <v>0.290982336535481</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>7</v>
       </c>
@@ -1253,7 +1280,7 @@
         <v>0.36523517382413001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>8</v>
       </c>
@@ -1474,7 +1501,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B43" s="4">
@@ -1499,14 +1526,14 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
@@ -1889,7 +1916,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B65" s="4">
@@ -1958,21 +1985,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2422,14 +2449,14 @@
       <c r="I22" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -2852,14 +2879,14 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
@@ -3323,16 +3350,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="F1" s="13" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13"/>
+      <c r="G1" s="12"/>
       <c r="I1" s="11" t="s">
         <v>46</v>
       </c>
@@ -3416,11 +3443,11 @@
         <v>0.60816326530612197</v>
       </c>
       <c r="C4" s="7">
-        <f t="shared" ref="C4:C22" si="0">B4-G4</f>
+        <f t="shared" ref="C4:C21" si="0">B4-G4</f>
         <v>-1.683673469387803E-2</v>
       </c>
       <c r="D4" s="7">
-        <f t="shared" ref="D4:D22" si="1">B4-M4</f>
+        <f t="shared" ref="D4:D21" si="1">B4-M4</f>
         <v>2.4829931972788932E-2</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -4025,12 +4052,12 @@
       <c r="D22"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -4070,7 +4097,7 @@
         <v>0.79220779220779203</v>
       </c>
       <c r="C26" s="7">
-        <f t="shared" ref="C26:C44" si="2">B26-G4</f>
+        <f t="shared" ref="C26:C43" si="2">B26-G4</f>
         <v>0.16720779220779203</v>
       </c>
       <c r="D26" s="7">
@@ -4355,12 +4382,12 @@
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -4725,6 +4752,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C1:D1 C3:D21 C23:D23 C25:D43 C45:D45 C47:D65 C1591:D1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F21">
     <cfRule type="colorScale" priority="53">
       <colorScale>
@@ -4747,6 +4785,38 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G21">
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="83">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4789,6 +4859,38 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J21">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="89">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L21">
     <cfRule type="colorScale" priority="17">
       <colorScale>
@@ -4811,70 +4913,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G21">
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="83">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4917,17 +4955,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:D1 C25:D43 C3:D21 C47:D65 C23:D23 C45:D45 C1591:D1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
+++ b/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\initial_testing_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4620F94D-D1ED-43F7-A824-990DBC4A20B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81240C69-8B45-404A-A16A-13B6E294F9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="58">
   <si>
     <t>Model</t>
   </si>
@@ -204,6 +204,15 @@
   <si>
     <t>MAX</t>
   </si>
+  <si>
+    <t>OG</t>
+  </si>
+  <si>
+    <t>Using JSON-repair</t>
+  </si>
+  <si>
+    <t>JSON-repair (only one response for TASKS was previously unparsable)</t>
+  </si>
 </sst>
 </file>
 
@@ -289,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -300,6 +309,12 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -309,10 +324,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -626,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F8CBD-665F-4514-96E7-546603B512CB}">
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -636,1317 +651,2418 @@
     <col min="5" max="5" width="13.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="14.140625" style="5" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="23.85546875" customWidth="1"/>
-    <col min="12" max="12" width="21.5703125" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="11" max="11" width="21.28515625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="18" style="5" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" style="5" customWidth="1"/>
+    <col min="14" max="15" width="13.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="J1" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="J2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="J3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7">
         <v>0.79975124378109397</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C4" s="7">
         <v>0.88324175824175799</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D4" s="7">
         <v>0.83942558746736295</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E4" s="7">
         <v>0.78304612706701404</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F4" s="7">
         <v>0.56790237588980297</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="J4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.79975124378109397</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.88324175824175799</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0.83942558746736295</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0.78304612706701404</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0.56790237588980297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B5" s="7">
         <v>0.82074263764404598</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C5" s="7">
         <v>0.88049450549450503</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D5" s="7">
         <v>0.84956925115970805</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E5" s="7">
         <v>0.80181604486479396</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F5" s="7">
         <v>0.60442987182720698</v>
       </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="J5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0.819108280254777</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0.88324175824175799</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0.84996695307336401</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0.80147966804919502</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0.60388492181939202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B6" s="7">
         <v>0.82845744680850997</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C6" s="7">
         <v>0.85576923076922995</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D6" s="7">
         <v>0.84189189189189095</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E6" s="7">
         <v>0.79804678628208003</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F6" s="7">
         <v>0.59625862695241505</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="J6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0.82891246684350095</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0.85851648351648302</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0.84345479082321095</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0.79962213225371104</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0.59943659412058703</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B7" s="7">
         <v>0.81430219146482097</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C7" s="6">
         <v>0.969780219780219</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D7" s="7">
         <v>0.88526645768025003</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E7" s="7">
         <v>0.83331423242435398</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F7" s="7">
         <v>0.67138435366112903</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="J7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.81430219146482097</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0.969780219780219</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.88526645768025003</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.83331423242435398</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0.67138435366112903</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B8" s="7">
         <v>0.77697841726618699</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C8" s="7">
         <v>0.59340659340659296</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D8" s="7">
         <v>0.67289719626168198</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E8" s="7">
         <v>0.65352176886254798</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F8" s="7">
         <v>0.320677619817825</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="J8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0.77697841726618699</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0.59340659340659296</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0.67289719626168198</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.65352176886254798</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0.320677619817825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B9" s="7">
         <v>0.79500891265597096</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C9" s="7">
         <v>0.61263736263736202</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D9" s="7">
         <v>0.69200930954228002</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E9" s="7">
         <v>0.67233886299511203</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F9" s="7">
         <v>0.35685204527529601</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="J9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.79500891265597096</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0.61263736263736202</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0.69200930954228002</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.67233886299511203</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0.35685204527529601</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B10" s="7">
         <v>0.80606060606060603</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C10" s="7">
         <v>0.73076923076922995</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D10" s="7">
         <v>0.76657060518731901</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E10" s="7">
         <v>0.72811288880055602</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F10" s="7">
         <v>0.45795544598045201</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="J10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.80606060606060603</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.73076923076922995</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0.76657060518731901</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.72811288880055602</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0.45795544598045201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B11" s="7">
         <v>0.79880239520957996</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C11" s="7">
         <v>0.91620879120879095</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D11" s="7">
         <v>0.85348688419705698</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E11" s="7">
         <v>0.79498279767965596</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F11" s="7">
         <v>0.59339298647290994</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.79928315412186302</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0.91895604395604302</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0.85495207667731599</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.79656485033404401</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0.59666144530428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="7">
         <v>0.84036144578313199</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C12" s="7">
         <v>0.76648351648351598</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D12" s="7">
         <v>0.80172413793103403</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E12" s="7">
         <v>0.76816976127320902</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F12" s="7">
         <v>0.53764768118497597</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="J12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.84036144578313199</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0.76648351648351598</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0.80172413793103403</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.76816976127320902</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0.53764768118497597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B13" s="7">
         <v>0.875</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C13" s="7">
         <v>0.75961538461538403</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D13" s="7">
         <v>0.81323529411764695</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E13" s="7">
         <v>0.78814749780509197</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F13" s="7">
         <v>0.57895655208515096</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="J13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0.75961538461538403</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0.81323529411764695</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0.78814749780509197</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0.57895655208515096</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B14" s="7">
         <v>0.85467625899280497</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C14" s="7">
         <v>0.81593406593406503</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D14" s="7">
         <v>0.83485593815881898</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="7">
         <v>0.80097603647286797</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F14" s="7">
         <v>0.60225374696568101</v>
       </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="J14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0.85467625899280497</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0.81593406593406503</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0.83485593815881898</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0.80097603647286797</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0.60225374696568101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B15" s="7">
         <v>0.78669724770642202</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C15" s="7">
         <v>0.94230769230769196</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D15" s="7">
         <v>0.85750000000000004</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E15" s="7">
         <v>0.79173076923076902</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F15" s="7">
         <v>0.58985040711986303</v>
       </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="J15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0.78669724770642202</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.94230769230769196</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.85750000000000004</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.79173076923076902</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0.58985040711986303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B16" s="7">
         <v>0.87835926449787805</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C16" s="7">
         <v>0.85302197802197799</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D16" s="7">
         <v>0.86550522648083605</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E16" s="7">
         <v>0.83596224212707804</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F16" s="7">
         <v>0.67202557967935905</v>
       </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="J16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.87835926449787805</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0.85302197802197799</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0.86550522648083605</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0.83596224212707804</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0.67202557967935905</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="7">
         <v>0.76005961251862797</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C17" s="7">
         <v>0.70054945054944995</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D17" s="7">
         <v>0.72909220872051395</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E17" s="7">
         <v>0.68109983136896901</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F17" s="7">
         <v>0.363630338245365</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="J17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0.75620437956204301</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0.71153846153846101</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0.73319179051663097</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0.68161061557234903</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0.36403791090493398</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B18" s="7">
         <v>0.80653266331658202</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C18" s="7">
         <v>0.88186813186813096</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D18" s="7">
         <v>0.84251968503937003</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E18" s="7">
         <v>0.789101252211315</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F18" s="7">
         <v>0.57960726468147805</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="J18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0.80653266331658202</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0.88186813186813096</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0.84251968503937003</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0.789101252211315</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0.57960726468147805</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B19" s="6">
         <v>0.89629629629629604</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C19" s="7">
         <v>0.83104395604395598</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D19" s="7">
         <v>0.86243763364219495</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E19" s="7">
         <v>0.83743844753052399</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="7">
         <v>0.67550826272592501</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="J19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0.89629629629629604</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.83104395604395598</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0.86243763364219495</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0.83743844753052399</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0.67550826272592501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B20" s="7">
         <v>0.86658195679796701</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C20" s="7">
         <v>0.93681318681318604</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D20" s="6">
         <v>0.90033003300329995</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E20" s="6">
         <v>0.86783131966413596</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F20" s="6">
         <v>0.73632332330032302</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="J20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0.86759142496847397</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.94505494505494503</v>
+      </c>
+      <c r="M20" s="4">
+        <v>0.90466798159105799</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0.87275111483504597</v>
+      </c>
+      <c r="O20" s="4">
+        <v>0.74627587318398403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B21" s="7">
         <v>0.88679245283018804</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C21" s="7">
         <v>0.64560439560439498</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D21" s="7">
         <v>0.74721780604133503</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E21" s="7">
         <v>0.73817449075490904</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F21" s="7">
         <v>0.48988982228038302</v>
       </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="J21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0.88786764705882304</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0.66346153846153799</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0.75943396226415005</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0.74782042940793703</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0.50695386702849299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="4">
-        <f>MAX(B3:B20)</f>
+      <c r="B22" s="4">
+        <f>MAX(B4:B21)</f>
         <v>0.89629629629629604</v>
       </c>
-      <c r="C21" s="4">
-        <f t="shared" ref="C21:F21" si="0">MAX(C3:C20)</f>
+      <c r="C22" s="4">
+        <f t="shared" ref="C22:F22" si="0">MAX(C4:C21)</f>
         <v>0.969780219780219</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D22" s="4">
         <f t="shared" si="0"/>
         <v>0.90033003300329995</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E22" s="4">
         <f t="shared" si="0"/>
         <v>0.86783131966413596</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F22" s="4">
         <f t="shared" si="0"/>
         <v>0.73632332330032302</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="J22" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="4">
+        <f>MAX(K4:K21)</f>
+        <v>0.89629629629629604</v>
+      </c>
+      <c r="L22" s="4">
+        <f t="shared" ref="L22:O22" si="1">MAX(L4:L21)</f>
+        <v>0.969780219780219</v>
+      </c>
+      <c r="M22" s="4">
+        <f t="shared" si="1"/>
+        <v>0.90466798159105799</v>
+      </c>
+      <c r="N22" s="4">
+        <f t="shared" si="1"/>
+        <v>0.87275111483504597</v>
+      </c>
+      <c r="O22" s="4">
+        <f t="shared" si="1"/>
+        <v>0.74627587318398403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="J24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="7">
+      <c r="J25" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7">
         <v>0.62935323383084496</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C26" s="7">
         <v>0.88771929824561402</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D26" s="7">
         <v>0.73653566229985401</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E26" s="7">
         <v>0.69719032642402901</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F26" s="7">
         <v>0.41636436920596498</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="J26" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0.62935323383084496</v>
+      </c>
+      <c r="L26" s="5">
+        <v>0.88771929824561402</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0.73653566229985401</v>
+      </c>
+      <c r="N26" s="5">
+        <v>0.69719032642402901</v>
+      </c>
+      <c r="O26" s="5">
+        <v>0.41636436920596498</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B27" s="7">
         <v>0.63252240717029395</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C27" s="7">
         <v>0.86666666666666603</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D27" s="7">
         <v>0.73131014063656496</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E27" s="7">
         <v>0.69775497781134399</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F27" s="7">
         <v>0.41339258660741302</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="J27" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0.63057324840764295</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0.86842105263157898</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0.73062730627306205</v>
+      </c>
+      <c r="N27" s="5">
+        <v>0.69586147114953001</v>
+      </c>
+      <c r="O27" s="5">
+        <v>0.41039878849066103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B28" s="7">
         <v>0.63430851063829696</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C28" s="7">
         <v>0.83684210526315705</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D28" s="7">
         <v>0.721633888048411</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E28" s="7">
         <v>0.69505117825843898</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="7">
         <v>0.40356564019448898</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="J28" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0.63395225464190896</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0.83859649122807001</v>
+      </c>
+      <c r="M28" s="5">
+        <v>0.722054380664652</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0.69496220838286704</v>
+      </c>
+      <c r="O28" s="5">
+        <v>0.40368644926068398</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B29" s="7">
         <v>0.62514417531718502</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C29" s="6">
         <v>0.95087719298245599</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D29" s="7">
         <v>0.75434933890048705</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E29" s="7">
         <v>0.69978773477687595</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F29" s="7">
         <v>0.43446480424551898</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="J29" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0.62514417531718502</v>
+      </c>
+      <c r="L29" s="4">
+        <v>0.95087719298245599</v>
+      </c>
+      <c r="M29" s="5">
+        <v>0.75434933890048705</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0.69978773477687595</v>
+      </c>
+      <c r="O29" s="5">
+        <v>0.43446480424551898</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B30" s="7">
         <v>0.60971223021582699</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C30" s="7">
         <v>0.59473684210526301</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D30" s="7">
         <v>0.60213143872113595</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E30" s="7">
         <v>0.62954963972810196</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F30" s="7">
         <v>0.25919801570897</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="J30" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0.60971223021582699</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.59473684210526301</v>
+      </c>
+      <c r="M30" s="5">
+        <v>0.60213143872113595</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0.62954963972810196</v>
+      </c>
+      <c r="O30" s="5">
+        <v>0.25919801570897</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B31" s="7">
         <v>0.62566844919786002</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C31" s="7">
         <v>0.61578947368421</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D31" s="7">
         <v>0.62068965517241304</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E31" s="7">
         <v>0.64547165310503796</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F31" s="7">
         <v>0.290982336535481</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="J31" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0.62566844919786002</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.61578947368421</v>
+      </c>
+      <c r="M31" s="5">
+        <v>0.62068965517241304</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.64547165310503796</v>
+      </c>
+      <c r="O31" s="5">
+        <v>0.290982336535481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B32" s="7">
         <v>0.63787878787878705</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C32" s="7">
         <v>0.73859649122807003</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D32" s="7">
         <v>0.68455284552845497</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E32" s="7">
         <v>0.68087875221514205</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F32" s="7">
         <v>0.36523517382413001</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="J32" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0.63787878787878705</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.73859649122807003</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0.68455284552845497</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0.68087875221514205</v>
+      </c>
+      <c r="O32" s="5">
+        <v>0.36523517382413001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B33" s="7">
         <v>0.62874251497005895</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C33" s="7">
         <v>0.92105263157894701</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D33" s="7">
         <v>0.74733096085409201</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E33" s="7">
         <v>0.70083198480873998</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F33" s="7">
         <v>0.42943244600703101</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="J33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0.627240143369175</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.92105263157894701</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0.74626865671641796</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0.69898798689479402</v>
+      </c>
+      <c r="O33" s="5">
+        <v>0.42633323290147601</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B34" s="7">
         <v>0.67319277108433695</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C34" s="7">
         <v>0.78421052631578902</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D34" s="7">
         <v>0.72447325769854098</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E34" s="7">
         <v>0.72033345689601502</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F34" s="7">
         <v>0.44399018806214202</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="J34" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0.67319277108433695</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.78421052631578902</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0.72447325769854098</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0.72033345689601502</v>
+      </c>
+      <c r="O34" s="5">
+        <v>0.44399018806214202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B35" s="7">
         <v>0.691455696202531</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C35" s="7">
         <v>0.76666666666666605</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D35" s="7">
         <v>0.72712146422628898</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E35" s="7">
         <v>0.73022739877981102</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F35" s="7">
         <v>0.461853978671041</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="J35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0.691455696202531</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.76666666666666605</v>
+      </c>
+      <c r="M35" s="5">
+        <v>0.72712146422628898</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0.73022739877981102</v>
+      </c>
+      <c r="O35" s="5">
+        <v>0.461853978671041</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B36" s="7">
         <v>0.66043165467625897</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C36" s="7">
         <v>0.80526315789473601</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D36" s="7">
         <v>0.725691699604743</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E36" s="7">
         <v>0.71417404174752996</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F36" s="7">
         <v>0.43433520122261798</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="J36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0.66043165467625897</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.80526315789473601</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0.725691699604743</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0.71417404174752996</v>
+      </c>
+      <c r="O36" s="5">
+        <v>0.43433520122261798</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B37" s="7">
         <v>0.61811926605504497</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C37" s="7">
         <v>0.94561403508771902</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D37" s="7">
         <v>0.74757281553398003</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E37" s="7">
         <v>0.68994802392860599</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F37" s="7">
         <v>0.417133706965572</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="J37" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="5">
+        <v>0.61811926605504497</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.94561403508771902</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0.74757281553398003</v>
+      </c>
+      <c r="N37" s="5">
+        <v>0.68994802392860599</v>
+      </c>
+      <c r="O37" s="5">
+        <v>0.417133706965572</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B38" s="6">
         <v>0.71145685997171104</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C38" s="7">
         <v>0.88245614035087705</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D38" s="6">
         <v>0.78778386844166004</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E38" s="6">
         <v>0.77657591690481198</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F38" s="6">
         <v>0.55876666327465097</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="J38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K38" s="4">
+        <v>0.71145685997171104</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.88245614035087705</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0.78778386844166004</v>
+      </c>
+      <c r="N38" s="4">
+        <v>0.77657591690481198</v>
+      </c>
+      <c r="O38" s="4">
+        <v>0.55876666327465097</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B39" s="7">
         <v>0.59910581222056603</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C39" s="7">
         <v>0.70526315789473604</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D39" s="7">
         <v>0.64786462530217503</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E39" s="7">
         <v>0.64047303473337103</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F39" s="7">
         <v>0.28587478296394597</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="J39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0.59562043795620401</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.71578947368420998</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0.650199203187251</v>
+      </c>
+      <c r="N39" s="5">
+        <v>0.63860852257918199</v>
+      </c>
+      <c r="O39" s="5">
+        <v>0.28363080061193202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B40" s="7">
         <v>0.62814070351758799</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C40" s="7">
         <v>0.87719298245613997</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D40" s="7">
         <v>0.73206442166910601</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E40" s="7">
         <v>0.69436241721353997</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F40" s="7">
         <v>0.40943929003630403</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="J40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.62814070351758799</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.87719298245613997</v>
+      </c>
+      <c r="M40" s="5">
+        <v>0.73206442166910601</v>
+      </c>
+      <c r="N40" s="5">
+        <v>0.69436241721353997</v>
+      </c>
+      <c r="O40" s="5">
+        <v>0.40943929003630403</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B41" s="7">
         <v>0.706666666666666</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C41" s="7">
         <v>0.83684210526315705</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D41" s="7">
         <v>0.76626506024096297</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E41" s="7">
         <v>0.76055460257203999</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F41" s="7">
         <v>0.52465543644716695</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="J41" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K41" s="5">
+        <v>0.706666666666666</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.83684210526315705</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0.76626506024096297</v>
+      </c>
+      <c r="N41" s="5">
+        <v>0.76055460257203999</v>
+      </c>
+      <c r="O41" s="5">
+        <v>0.52465543644716695</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B42" s="7">
         <v>0.677255400254129</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C42" s="7">
         <v>0.93508771929824497</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D42" s="7">
         <v>0.78555637435519499</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E42" s="7">
         <v>0.75742934996829503</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F42" s="7">
         <v>0.530029272231755</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="J42" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.679697351828499</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.94561403508771902</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0.79090242112985998</v>
+      </c>
+      <c r="N42" s="5">
+        <v>0.76214905902143104</v>
+      </c>
+      <c r="O42" s="5">
+        <v>0.53999798244729103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B43" s="7">
         <v>0.70754716981132004</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C43" s="7">
         <v>0.65789473684210498</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D43" s="7">
         <v>0.68181818181818099</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E43" s="7">
         <v>0.70952770952770905</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F43" s="7">
         <v>0.419689119170984</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="J43" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0.71139705882352899</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0.67894736842105197</v>
+      </c>
+      <c r="M43" s="5">
+        <v>0.694793536804308</v>
+      </c>
+      <c r="N43" s="5">
+        <v>0.71841346035966502</v>
+      </c>
+      <c r="O43" s="5">
+        <v>0.43708609271523102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="4">
-        <f>MAX(B25:B42)</f>
+      <c r="B44" s="4">
+        <f>MAX(B26:B43)</f>
         <v>0.71145685997171104</v>
       </c>
-      <c r="C43" s="4">
-        <f t="shared" ref="C43:F43" si="1">MAX(C25:C42)</f>
+      <c r="C44" s="4">
+        <f t="shared" ref="C44:F44" si="2">MAX(C26:C43)</f>
         <v>0.95087719298245599</v>
       </c>
-      <c r="D43" s="4">
-        <f t="shared" si="1"/>
+      <c r="D44" s="4">
+        <f t="shared" si="2"/>
         <v>0.78778386844166004</v>
       </c>
-      <c r="E43" s="4">
-        <f t="shared" si="1"/>
+      <c r="E44" s="4">
+        <f t="shared" si="2"/>
         <v>0.77657591690481198</v>
       </c>
-      <c r="F43" s="4">
-        <f t="shared" si="1"/>
+      <c r="F44" s="4">
+        <f t="shared" si="2"/>
         <v>0.55876666327465097</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
+      <c r="J44" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K44" s="4">
+        <f>MAX(K26:K43)</f>
+        <v>0.71145685997171104</v>
+      </c>
+      <c r="L44" s="4">
+        <f t="shared" ref="L44:O44" si="3">MAX(L26:L43)</f>
+        <v>0.95087719298245599</v>
+      </c>
+      <c r="M44" s="4">
+        <f t="shared" si="3"/>
+        <v>0.79090242112985998</v>
+      </c>
+      <c r="N44" s="4">
+        <f t="shared" si="3"/>
+        <v>0.77657591690481198</v>
+      </c>
+      <c r="O44" s="4">
+        <f t="shared" si="3"/>
+        <v>0.55876666327465097</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="J46" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F47" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B47" s="7">
+      <c r="J47" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="7">
         <v>0.83955223880596996</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C48" s="7">
         <v>0.84586466165413499</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D48" s="7">
         <v>0.84269662921348298</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E48" s="7">
         <v>0.76954108569107804</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F48" s="7">
         <v>0.53909465020576097</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="J48" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K48" s="5">
+        <v>0.83955223880596996</v>
+      </c>
+      <c r="L48" s="5">
+        <v>0.84586466165413499</v>
+      </c>
+      <c r="M48" s="5">
+        <v>0.84269662921348298</v>
+      </c>
+      <c r="N48" s="5">
+        <v>0.76954108569107804</v>
+      </c>
+      <c r="O48" s="5">
+        <v>0.53909465020576097</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B49" s="7">
         <v>0.84379001280409704</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C49" s="7">
         <v>0.825814536340852</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D49" s="7">
         <v>0.83470550981633895</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E49" s="7">
         <v>0.76436330590465196</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F49" s="7">
         <v>0.52882771070743495</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="J49" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0.84203821656050903</v>
+      </c>
+      <c r="L49" s="5">
+        <v>0.82832080200501201</v>
+      </c>
+      <c r="M49" s="5">
+        <v>0.83512318382817397</v>
+      </c>
+      <c r="N49" s="5">
+        <v>0.76385134456426296</v>
+      </c>
+      <c r="O49" s="5">
+        <v>0.52776207169512601</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B50" s="7">
         <v>0.84840425531914898</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C50" s="7">
         <v>0.79949874686716704</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D50" s="7">
         <v>0.82322580645161203</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E50" s="7">
         <v>0.75628410503986498</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F50" s="7">
         <v>0.51332149200710397</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="J50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="K50" s="5">
+        <v>0.84880636604774495</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0.80200501253132805</v>
+      </c>
+      <c r="M50" s="5">
+        <v>0.82474226804123696</v>
+      </c>
+      <c r="N50" s="5">
+        <v>0.75782567947516399</v>
+      </c>
+      <c r="O50" s="5">
+        <v>0.51633696376972604</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B51" s="7">
         <v>0.84659746251441703</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C51" s="6">
         <v>0.91979949874686695</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D51" s="7">
         <v>0.88168168168168104</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E51" s="7">
         <v>0.81241841580824603</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F51" s="7">
         <v>0.62623028578204598</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="J51" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0.84659746251441703</v>
+      </c>
+      <c r="L51" s="4">
+        <v>0.91979949874686695</v>
+      </c>
+      <c r="M51" s="5">
+        <v>0.88168168168168104</v>
+      </c>
+      <c r="N51" s="5">
+        <v>0.81241841580824603</v>
+      </c>
+      <c r="O51" s="5">
+        <v>0.62623028578204598</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B52" s="7">
         <v>0.79856115107913594</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C52" s="7">
         <v>0.55639097744360899</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D52" s="7">
         <v>0.65583456425406195</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E52" s="7">
         <v>0.61177628027174302</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F52" s="7">
         <v>0.25350420504605498</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="J52" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0.79856115107913594</v>
+      </c>
+      <c r="L52" s="5">
+        <v>0.55639097744360899</v>
+      </c>
+      <c r="M52" s="5">
+        <v>0.65583456425406195</v>
+      </c>
+      <c r="N52" s="5">
+        <v>0.61177628027174302</v>
+      </c>
+      <c r="O52" s="5">
+        <v>0.25350420504605498</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B53" s="7">
         <v>0.81639928698752195</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C53" s="7">
         <v>0.57393483709273097</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D53" s="7">
         <v>0.67402501839587903</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E53" s="7">
         <v>0.63058194069840501</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F53" s="7">
         <v>0.28856770049181901</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="J53" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0.81639928698752195</v>
+      </c>
+      <c r="L53" s="5">
+        <v>0.57393483709273097</v>
+      </c>
+      <c r="M53" s="5">
+        <v>0.67402501839587903</v>
+      </c>
+      <c r="N53" s="5">
+        <v>0.63058194069840501</v>
+      </c>
+      <c r="O53" s="5">
+        <v>0.28856770049181901</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B54" s="7">
         <v>0.85303030303030303</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C54" s="7">
         <v>0.70551378446115198</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D54" s="7">
         <v>0.772290809327846</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E54" s="7">
         <v>0.715714193164949</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F54" s="7">
         <v>0.43895226024503498</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="J54" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0.85303030303030303</v>
+      </c>
+      <c r="L54" s="5">
+        <v>0.70551378446115198</v>
+      </c>
+      <c r="M54" s="5">
+        <v>0.772290809327846</v>
+      </c>
+      <c r="N54" s="5">
+        <v>0.715714193164949</v>
+      </c>
+      <c r="O54" s="5">
+        <v>0.43895226024503498</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B55" s="7">
         <v>0.84910179640718497</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C55" s="7">
         <v>0.88847117794486197</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D55" s="7">
         <v>0.86834047764849898</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E55" s="7">
         <v>0.79962705985053195</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F55" s="7">
         <v>0.59967415338065799</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="J55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0.84946236559139698</v>
+      </c>
+      <c r="L55" s="5">
+        <v>0.89097744360902198</v>
+      </c>
+      <c r="M55" s="5">
+        <v>0.86972477064220099</v>
+      </c>
+      <c r="N55" s="5">
+        <v>0.80123628745409903</v>
+      </c>
+      <c r="O55" s="5">
+        <v>0.60293603635092596</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B56" s="7">
         <v>0.86445783132530096</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C56" s="7">
         <v>0.71929824561403499</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D56" s="7">
         <v>0.78522571819425402</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E56" s="7">
         <v>0.73075718899403397</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F56" s="7">
         <v>0.46824724809483398</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="J56" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0.86445783132530096</v>
+      </c>
+      <c r="L56" s="5">
+        <v>0.71929824561403499</v>
+      </c>
+      <c r="M56" s="5">
+        <v>0.78522571819425402</v>
+      </c>
+      <c r="N56" s="5">
+        <v>0.73075718899403397</v>
+      </c>
+      <c r="O56" s="5">
+        <v>0.46824724809483398</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B57" s="7">
         <v>0.873417721518987</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C57" s="7">
         <v>0.69172932330826997</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D57" s="7">
         <v>0.77202797202797202</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E57" s="7">
         <v>0.72333933531538297</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F57" s="7">
         <v>0.45711906744379599</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="J57" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0.873417721518987</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0.69172932330826997</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0.77202797202797202</v>
+      </c>
+      <c r="N57" s="5">
+        <v>0.72333933531538297</v>
+      </c>
+      <c r="O57" s="5">
+        <v>0.45711906744379599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B58" s="7">
         <v>0.87194244604316495</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C58" s="7">
         <v>0.75939849624060096</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D58" s="7">
         <v>0.81178834561285995</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E58" s="7">
         <v>0.75626690976063604</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F58" s="7">
         <v>0.51619498547293596</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="J58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0.87194244604316495</v>
+      </c>
+      <c r="L58" s="5">
+        <v>0.75939849624060096</v>
+      </c>
+      <c r="M58" s="5">
+        <v>0.81178834561285995</v>
+      </c>
+      <c r="N58" s="5">
+        <v>0.75626690976063604</v>
+      </c>
+      <c r="O58" s="5">
+        <v>0.51619498547293596</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B59" s="7">
         <v>0.84059633027522895</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C59" s="7">
         <v>0.918546365914787</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D59" s="7">
         <v>0.87784431137724495</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E59" s="7">
         <v>0.80506388797208694</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F59" s="7">
         <v>0.61179828734538499</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="J59" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K59" s="5">
+        <v>0.84059633027522895</v>
+      </c>
+      <c r="L59" s="5">
+        <v>0.918546365914787</v>
+      </c>
+      <c r="M59" s="5">
+        <v>0.87784431137724495</v>
+      </c>
+      <c r="N59" s="5">
+        <v>0.80506388797208694</v>
+      </c>
+      <c r="O59" s="5">
+        <v>0.61179828734538499</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B60" s="7">
         <v>0.88684582743988605</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C60" s="7">
         <v>0.78571428571428503</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D60" s="7">
         <v>0.83322259136212595</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E60" s="7">
         <v>0.78122833990975704</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F60" s="7">
         <v>0.56503844904148104</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="J60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K60" s="5">
+        <v>0.88684582743988605</v>
+      </c>
+      <c r="L60" s="5">
+        <v>0.78571428571428503</v>
+      </c>
+      <c r="M60" s="5">
+        <v>0.83322259136212595</v>
+      </c>
+      <c r="N60" s="5">
+        <v>0.78122833990975704</v>
+      </c>
+      <c r="O60" s="5">
+        <v>0.56503844904148104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B61" s="7">
         <v>0.81669150521609502</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C61" s="7">
         <v>0.68671679197994895</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D61" s="7">
         <v>0.74608577263444498</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E61" s="7">
         <v>0.67937725807215499</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F61" s="7">
         <v>0.36598321470306999</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="J61" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0.81313868613138596</v>
+      </c>
+      <c r="L61" s="5">
+        <v>0.69799498746867095</v>
+      </c>
+      <c r="M61" s="5">
+        <v>0.75118004045853004</v>
+      </c>
+      <c r="N61" s="5">
+        <v>0.68117484636203596</v>
+      </c>
+      <c r="O61" s="5">
+        <v>0.36808305683399301</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B62" s="7">
         <v>0.84673366834170805</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C62" s="7">
         <v>0.84461152882205504</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D62" s="7">
         <v>0.84567126725219499</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E62" s="7">
         <v>0.77605759066667002</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F62" s="7">
         <v>0.55211652253072296</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="J62" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" s="5">
+        <v>0.84673366834170805</v>
+      </c>
+      <c r="L62" s="5">
+        <v>0.84461152882205504</v>
+      </c>
+      <c r="M62" s="5">
+        <v>0.84567126725219499</v>
+      </c>
+      <c r="N62" s="5">
+        <v>0.77605759066667002</v>
+      </c>
+      <c r="O62" s="5">
+        <v>0.55211652253072296</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B63" s="6">
         <v>0.91259259259259196</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C63" s="7">
         <v>0.77192982456140302</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D63" s="7">
         <v>0.83638832315003397</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E63" s="7">
         <v>0.79254244103278504</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F63" s="7">
         <v>0.58948152879804105</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="J63" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K63" s="4">
+        <v>0.91259259259259196</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0.77192982456140302</v>
+      </c>
+      <c r="M63" s="5">
+        <v>0.83638832315003397</v>
+      </c>
+      <c r="N63" s="5">
+        <v>0.79254244103278504</v>
+      </c>
+      <c r="O63" s="5">
+        <v>0.58948152879804105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B64" s="7">
         <v>0.89199491740787795</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C64" s="7">
         <v>0.87969924812029998</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D64" s="6">
         <v>0.88580441640378504</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E64" s="6">
         <v>0.83605451044510404</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F64" s="6">
         <v>0.67213857126683996</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="J64" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0.89155107187894</v>
+      </c>
+      <c r="L64" s="5">
+        <v>0.88596491228070096</v>
+      </c>
+      <c r="M64" s="4">
+        <v>0.88874921433060905</v>
+      </c>
+      <c r="N64" s="4">
+        <v>0.83914274034009595</v>
+      </c>
+      <c r="O64" s="4">
+        <v>0.67829149153697599</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B65" s="7">
         <v>0.87735849056603699</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C65" s="7">
         <v>0.58270676691729295</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D65" s="7">
         <v>0.70030120481927705</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E65" s="7">
         <v>0.66989697922123204</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F65" s="7">
         <v>0.37062660604862602</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
+      <c r="J65" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0.88051470588235203</v>
+      </c>
+      <c r="L65" s="5">
+        <v>0.60025062656641603</v>
+      </c>
+      <c r="M65" s="5">
+        <v>0.713859910581222</v>
+      </c>
+      <c r="N65" s="5">
+        <v>0.68078316629978497</v>
+      </c>
+      <c r="O65" s="5">
+        <v>0.38853503184713301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B65" s="4">
-        <f>MAX(B47:B64)</f>
+      <c r="B66" s="4">
+        <f>MAX(B48:B65)</f>
         <v>0.91259259259259196</v>
       </c>
-      <c r="C65" s="4">
-        <f t="shared" ref="C65:F65" si="2">MAX(C47:C64)</f>
+      <c r="C66" s="4">
+        <f t="shared" ref="C66:F66" si="4">MAX(C48:C65)</f>
         <v>0.91979949874686695</v>
       </c>
-      <c r="D65" s="4">
-        <f t="shared" si="2"/>
+      <c r="D66" s="4">
+        <f t="shared" si="4"/>
         <v>0.88580441640378504</v>
       </c>
-      <c r="E65" s="4">
-        <f t="shared" si="2"/>
+      <c r="E66" s="4">
+        <f t="shared" si="4"/>
         <v>0.83605451044510404</v>
       </c>
-      <c r="F65" s="4">
-        <f t="shared" si="2"/>
+      <c r="F66" s="4">
+        <f t="shared" si="4"/>
         <v>0.67213857126683996</v>
       </c>
+      <c r="J66" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K66" s="4">
+        <f>MAX(K48:K65)</f>
+        <v>0.91259259259259196</v>
+      </c>
+      <c r="L66" s="4">
+        <f t="shared" ref="L66:O66" si="5">MAX(L48:L65)</f>
+        <v>0.91979949874686695</v>
+      </c>
+      <c r="M66" s="4">
+        <f t="shared" si="5"/>
+        <v>0.88874921433060905</v>
+      </c>
+      <c r="N66" s="4">
+        <f t="shared" si="5"/>
+        <v>0.83914274034009595</v>
+      </c>
+      <c r="O66" s="4">
+        <f t="shared" si="5"/>
+        <v>0.67829149153697599</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="J24:O24"/>
+    <mergeCell ref="J46:O46"/>
+    <mergeCell ref="J1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:F1048576">
+  <conditionalFormatting sqref="B2:F1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:O66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1965,7 +3081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01ECBC17-39A9-4D61-99CF-DD2438BA63A7}">
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="2" customWidth="1"/>
@@ -1985,1336 +3101,2515 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="I1" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="I2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.96363636363636296</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0.98148148148148096</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0.94074074074073999</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.88170055452865004</v>
-      </c>
-      <c r="I3" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="5">
-        <v>0.28571428571428498</v>
+        <v>0.96363636363636296</v>
       </c>
       <c r="C4" s="5">
-        <v>0.66666666666666596</v>
+        <v>1</v>
       </c>
       <c r="D4" s="5">
-        <v>0.4</v>
+        <v>0.98148148148148096</v>
       </c>
       <c r="E4" s="5">
-        <v>0.60816326530612197</v>
+        <v>0.94074074074073999</v>
       </c>
       <c r="F4" s="5">
-        <v>0.25291828793774301</v>
-      </c>
-      <c r="I4" s="4"/>
+        <v>0.88170055452865004</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0.96363636363636296</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0.98148148148148096</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0.94074074074073999</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0.88170055452865004</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="5">
-        <v>0.8</v>
+        <v>0.28571428571428498</v>
       </c>
       <c r="C5" s="5">
         <v>0.66666666666666596</v>
       </c>
       <c r="D5" s="5">
-        <v>0.72727272727272696</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="5">
-        <v>0.81626794258373203</v>
+        <v>0.60816326530612197</v>
       </c>
       <c r="F5" s="5">
-        <v>0.63358778625954204</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>0.25291828793774301</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0.60816326530612197</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0.25291828793774301</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5">
-        <v>0.83673469387755095</v>
+        <v>0.8</v>
       </c>
       <c r="C6" s="5">
-        <v>1</v>
+        <v>0.66666666666666596</v>
       </c>
       <c r="D6" s="5">
-        <v>0.91111111111111098</v>
+        <v>0.72727272727272696</v>
       </c>
       <c r="E6" s="5">
-        <v>0.85029239766081799</v>
+        <v>0.81626794258373203</v>
       </c>
       <c r="F6" s="5">
-        <v>0.70608495981630304</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>0.63358778625954204</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0.81626794258373203</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0.63358778625954204</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5">
-        <v>0.84375</v>
+        <v>0.83673469387755095</v>
       </c>
       <c r="C7" s="5">
-        <v>0.96428571428571397</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5">
-        <v>0.9</v>
+        <v>0.91111111111111098</v>
       </c>
       <c r="E7" s="5">
-        <v>0.90588235294117603</v>
+        <v>0.85029239766081799</v>
       </c>
       <c r="F7" s="5">
-        <v>0.8125</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>0.70608495981630304</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.83673469387755095</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.91111111111111098</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.85029239766081799</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.70608495981630304</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="5">
-        <v>0.9375</v>
+        <v>0.84375</v>
       </c>
       <c r="C8" s="5">
-        <v>0.88235294117647001</v>
+        <v>0.96428571428571397</v>
       </c>
       <c r="D8" s="5">
-        <v>0.90909090909090895</v>
+        <v>0.9</v>
       </c>
       <c r="E8" s="5">
-        <v>0.79937304075235105</v>
+        <v>0.90588235294117603</v>
       </c>
       <c r="F8" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>0.8125</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.84375</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0.96428571428571397</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0.90588235294117603</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.8125</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5">
-        <v>0.95348837209302295</v>
+        <v>0.9375</v>
       </c>
       <c r="C9" s="5">
-        <v>0.80392156862745101</v>
+        <v>0.88235294117647001</v>
       </c>
       <c r="D9" s="5">
-        <v>0.87234042553191404</v>
+        <v>0.90909090909090895</v>
       </c>
       <c r="E9" s="5">
-        <v>0.75969962453066298</v>
+        <v>0.79937304075235105</v>
       </c>
       <c r="F9" s="5">
-        <v>0.52883435582822003</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>0.6</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.88235294117647001</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0.90909090909090895</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0.79937304075235105</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5">
-        <v>0.98076923076922995</v>
+        <v>0.95348837209302295</v>
       </c>
       <c r="C10" s="5">
-        <v>0.98076923076922995</v>
+        <v>0.80392156862745101</v>
       </c>
       <c r="D10" s="5">
-        <v>0.98076923076922995</v>
+        <v>0.87234042553191404</v>
       </c>
       <c r="E10" s="5">
-        <v>0.94871794871794801</v>
+        <v>0.75969962453066298</v>
       </c>
       <c r="F10" s="5">
-        <v>0.89743589743589702</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>0.52883435582822003</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.95348837209302295</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.80392156862745101</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.87234042553191404</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0.75969962453066298</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.52883435582822003</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="5">
-        <v>0.72093023255813904</v>
+        <v>0.98076923076922995</v>
       </c>
       <c r="C11" s="5">
-        <v>0.81578947368420995</v>
+        <v>0.98076923076922995</v>
       </c>
       <c r="D11" s="5">
-        <v>0.76543209876543195</v>
+        <v>0.98076923076922995</v>
       </c>
       <c r="E11" s="5">
-        <v>0.68058838980824699</v>
+        <v>0.94871794871794801</v>
       </c>
       <c r="F11" s="5">
-        <v>0.36534446764091799</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>0.89743589743589702</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0.98076923076922995</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.98076923076922995</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0.98076923076922995</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0.94871794871794801</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.89743589743589702</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="5">
-        <v>1</v>
+        <v>0.72093023255813904</v>
       </c>
       <c r="C12" s="5">
-        <v>0.97959183673469297</v>
+        <v>0.81578947368420995</v>
       </c>
       <c r="D12" s="5">
-        <v>0.98969072164948402</v>
+        <v>0.76543209876543195</v>
       </c>
       <c r="E12" s="5">
-        <v>0.97871632856667701</v>
+        <v>0.68058838980824699</v>
       </c>
       <c r="F12" s="5">
-        <v>0.95744680851063801</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>0.36534446764091799</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0.72093023255813904</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.81578947368420995</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0.76543209876543195</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0.68058838980824699</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.36534446764091799</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5">
         <v>1</v>
       </c>
       <c r="C13" s="5">
-        <v>0.98039215686274495</v>
+        <v>0.97959183673469297</v>
       </c>
       <c r="D13" s="5">
-        <v>0.99009900990098998</v>
+        <v>0.98969072164948402</v>
       </c>
       <c r="E13" s="5">
-        <v>0.976530986431976</v>
+        <v>0.97871632856667701</v>
       </c>
       <c r="F13" s="5">
-        <v>0.95307917888562999</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>0.95744680851063801</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="5">
-        <v>0.52272727272727204</v>
+        <v>1</v>
       </c>
       <c r="C14" s="5">
-        <v>0.85185185185185097</v>
+        <v>0.98039215686274495</v>
       </c>
       <c r="D14" s="5">
-        <v>0.647887323943662</v>
+        <v>0.99009900990098998</v>
       </c>
       <c r="E14" s="5">
-        <v>0.60464541635779501</v>
+        <v>0.976530986431976</v>
       </c>
       <c r="F14" s="5">
-        <v>0.26199261992619899</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>0.95307917888562999</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="5">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5">
-        <v>1</v>
+        <v>0.52272727272727204</v>
       </c>
       <c r="C15" s="5">
-        <v>0.98245614035087703</v>
+        <v>0.85185185185185097</v>
       </c>
       <c r="D15" s="5">
-        <v>0.99115044247787598</v>
+        <v>0.647887323943662</v>
       </c>
       <c r="E15" s="5">
-        <v>0.96224188790560405</v>
+        <v>0.60464541635779501</v>
       </c>
       <c r="F15" s="5">
-        <v>0.92452830188679203</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>0.26199261992619899</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0.53333333333333299</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.61904761904761896</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.29476584022038499</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.98245614035087703</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.99115044247787598</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.96224188790560405</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0.92452830188679203</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C17" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D17" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E17" s="5">
         <v>0.87070707070706999</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F17" s="5">
         <v>0.74141414141414097</v>
       </c>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="I17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0.96428571428571397</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0.98181818181818103</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0.89825119236883899</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0.79661016949152497</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B18" s="5">
         <v>0.88135593220338904</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C18" s="5">
         <v>0.98113207547169801</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D18" s="5">
         <v>0.92857142857142805</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E18" s="5">
         <v>0.71428571428571397</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F18" s="5">
         <v>0.439824945295404</v>
       </c>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="I18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0.88333333333333297</v>
+      </c>
+      <c r="K18" s="5">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0.93805309734513198</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0.73569321533923304</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0.48623853211009099</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B19" s="5">
         <v>0.74545454545454504</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C19" s="5">
         <v>0.95348837209302295</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D19" s="5">
         <v>0.83673469387755095</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E19" s="5">
         <v>0.65170068027210803</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F19" s="5">
         <v>0.33592736705577098</v>
       </c>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="I19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0.74545454545454504</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0.95348837209302295</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.83673469387755095</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0.65170068027210803</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0.33592736705577098</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B20" s="5">
         <v>0.94736842105263097</v>
       </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="5">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
         <v>0.97297297297297303</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E20" s="5">
         <v>0.98099198099198104</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F20" s="5">
         <v>0.96199524940617498</v>
       </c>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="I20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0.98099198099198104</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0.96199524940617498</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B21" s="5">
         <v>0.81818181818181801</v>
       </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
         <v>0.9</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E21" s="5">
         <v>0.92727272727272703</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F21" s="5">
         <v>0.855203619909502</v>
       </c>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="I21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0.92727272727272703</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0.855203619909502</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B22" s="5">
         <v>0.76190476190476097</v>
       </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
         <v>0.86486486486486402</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E22" s="5">
         <v>0.90495990495990497</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F22" s="5">
         <v>0.81132075471698095</v>
       </c>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="I22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0.76190476190476097</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.86486486486486402</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0.90495990495990497</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0.81132075471698095</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B23" s="5">
         <v>0.84016591020049303</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C23" s="5">
         <v>0.91963163467777098</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D23" s="5">
         <v>0.87016346346936801</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E23" s="5">
         <v>0.83588307372596604</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F23" s="5">
         <v>0.68005996297129001</v>
       </c>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="I23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0.84086237401024899</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0.92656040550928898</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0.873671750143314</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0.843560159120748</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0.69581409696619501</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="I25" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="I26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B27" s="5">
         <v>0.74545454545454504</v>
       </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="5">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5">
         <v>0.85416666666666596</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E27" s="5">
         <v>0.70833333333333304</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F27" s="5">
         <v>0.45165238678090502</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="I27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0.74545454545454504</v>
+      </c>
+      <c r="K27" s="5">
+        <v>1</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0.85416666666666596</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="N27" s="5">
+        <v>0.45165238678090502</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B28" s="5">
         <v>0.76190476190476097</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C28" s="5">
         <v>0.69565217391304301</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D28" s="5">
         <v>0.72727272727272696</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E28" s="5">
         <v>0.79220779220779203</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F28" s="5">
         <v>0.584864864864864</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="I28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0.76190476190476097</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0.69565217391304301</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="M28" s="5">
+        <v>0.79220779220779203</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0.584864864864864</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B29" s="5">
         <v>0.66666666666666596</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C29" s="5">
         <v>0.52631578947368396</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D29" s="5">
         <v>0.58823529411764697</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E29" s="5">
         <v>0.71964956195244001</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F29" s="5">
         <v>0.44209215442092098</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="I29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0.52631578947368396</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0.58823529411764697</v>
+      </c>
+      <c r="M29" s="5">
+        <v>0.71964956195244001</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0.44209215442092098</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B30" s="5">
         <v>0.183673469387755</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C30" s="5">
         <v>0.81818181818181801</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D30" s="5">
         <v>0.3</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E30" s="5">
         <v>0.34117647058823503</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F30" s="5">
         <v>2.67921795800144E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="I30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="5">
+        <v>0.183673469387755</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="M30" s="5">
+        <v>0.34117647058823503</v>
+      </c>
+      <c r="N30" s="5">
+        <v>2.67921795800144E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B31" s="5">
         <v>0.5625</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C31" s="5">
         <v>0.94736842105263097</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D31" s="5">
         <v>0.70588235294117596</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E31" s="5">
         <v>0.75553857906799005</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F31" s="5">
         <v>0.53125</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="I31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.70588235294117596</v>
+      </c>
+      <c r="M31" s="5">
+        <v>0.75553857906799005</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B32" s="5">
         <v>0.60416666666666596</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C32" s="5">
         <v>0.93548387096774099</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D32" s="5">
         <v>0.734177215189873</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E32" s="5">
         <v>0.65280289330922203</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F32" s="5">
         <v>0.35384615384615298</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="I32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0.60416666666666596</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0.93548387096774099</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.734177215189873</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0.65280289330922203</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0.35384615384615298</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B33" s="5">
         <v>0.51162790697674398</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C33" s="5">
         <v>0.84615384615384603</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D33" s="5">
         <v>0.63768115942028902</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E33" s="5">
         <v>0.606976172930483</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F33" s="5">
         <v>0.26605504587155898</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="I33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0.51162790697674398</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0.84615384615384603</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.63768115942028902</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0.606976172930483</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0.26605504587155898</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B34" s="5">
         <v>0.67307692307692302</v>
       </c>
-      <c r="C33" s="5">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
         <v>0.80459770114942497</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E34" s="5">
         <v>0.69498177740398004</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F34" s="5">
         <v>0.43568464730290402</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="I34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0.67307692307692302</v>
+      </c>
+      <c r="K34" s="5">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.80459770114942497</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0.69498177740398004</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0.43568464730290402</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B35" s="5">
         <v>0.53488372093023195</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C35" s="5">
         <v>0.88461538461538403</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D35" s="5">
         <v>0.66666666666666596</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E35" s="5">
         <v>0.63841807909604498</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F35" s="5">
         <v>0.32477064220183399</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="I35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0.53488372093023195</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0.88461538461538403</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="M35" s="5">
+        <v>0.63841807909604498</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0.32477064220183399</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="C35" s="5">
+      <c r="B36" s="5">
+        <v>1</v>
+      </c>
+      <c r="C36" s="5">
         <v>0.97959183673469297</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D36" s="5">
         <v>0.98969072164948402</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E36" s="5">
         <v>0.97871632856667701</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F36" s="5">
         <v>0.95744680851063801</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="I36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="5">
+        <v>1</v>
+      </c>
+      <c r="K36" s="5">
+        <v>1</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1</v>
+      </c>
+      <c r="M36" s="5">
+        <v>1</v>
+      </c>
+      <c r="N36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="5">
-        <v>1</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="C37" s="5">
         <v>0.98039215686274495</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D37" s="5">
         <v>0.99009900990098998</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E37" s="5">
         <v>0.976530986431976</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F37" s="5">
         <v>0.95307917888562999</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="I37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="5">
+        <v>1</v>
+      </c>
+      <c r="K37" s="5">
+        <v>1</v>
+      </c>
+      <c r="L37" s="5">
+        <v>1</v>
+      </c>
+      <c r="M37" s="5">
+        <v>1</v>
+      </c>
+      <c r="N37" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B38" s="5">
         <v>0.15909090909090901</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C38" s="5">
         <v>0.875</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D38" s="5">
         <v>0.269230769230769</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E38" s="5">
         <v>0.38461538461538403</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F38" s="5">
         <v>7.3170731707316999E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="I38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0.17777777777777701</v>
+      </c>
+      <c r="K38" s="5">
+        <v>1</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.30188679245283001</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0.40427672955974803</v>
+      </c>
+      <c r="N38" s="5">
+        <v>0.11377245508981999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B39" s="5">
         <v>0.94642857142857095</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C39" s="5">
         <v>0.98148148148148096</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D39" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E39" s="5">
         <v>0.87070707070706999</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F39" s="5">
         <v>0.74193548387096697</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="I39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="K39" s="5">
+        <v>1</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0.89825119236883899</v>
+      </c>
+      <c r="N39" s="5">
+        <v>0.797468354430379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B40" s="5">
         <v>0.98181818181818103</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C40" s="5">
         <v>0.96428571428571397</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D40" s="5">
         <v>0.97297297297297303</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E40" s="5">
         <v>0.89825119236883899</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F40" s="5">
         <v>0.79661016949152497</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="I40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J40" s="5">
+        <v>0.98214285714285698</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.98214285714285698</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.98214285714285698</v>
+      </c>
+      <c r="M40" s="5">
+        <v>0.92857142857142805</v>
+      </c>
+      <c r="N40" s="5">
+        <v>0.85714285714285698</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B41" s="5">
         <v>0.677966101694915</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C41" s="5">
         <v>0.97560975609756095</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D41" s="5">
         <v>0.8</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E41" s="5">
         <v>0.54285714285714204</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F41" s="5">
         <v>0.18053777208706701</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="I41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" s="5">
+        <v>0.68333333333333302</v>
+      </c>
+      <c r="K41" s="5">
+        <v>1</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.81188118811881105</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0.554088742207554</v>
+      </c>
+      <c r="N41" s="5">
+        <v>0.21243523316062099</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B42" s="5">
         <v>0.63636363636363602</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C42" s="5">
         <v>0.97222222222222199</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D42" s="5">
         <v>0.76923076923076905</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E42" s="5">
         <v>0.60083160083160003</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F42" s="5">
         <v>0.27896995708154498</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="I42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J42" s="5">
+        <v>0.63636363636363602</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.97222222222222199</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.76923076923076905</v>
+      </c>
+      <c r="M42" s="5">
+        <v>0.60083160083160003</v>
+      </c>
+      <c r="N42" s="5">
+        <v>0.27896995708154498</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B43" s="5">
         <v>0.73684210526315697</v>
       </c>
-      <c r="C42" s="5">
-        <v>1</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C43" s="5">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5">
         <v>0.84848484848484795</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E43" s="5">
         <v>0.89792663476874002</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F43" s="5">
         <v>0.797468354430379</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J43" s="5">
+        <v>0.73684210526315697</v>
+      </c>
+      <c r="K43" s="5">
+        <v>1</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0.84848484848484795</v>
+      </c>
+      <c r="M43" s="5">
+        <v>0.89792663476874002</v>
+      </c>
+      <c r="N43" s="5">
+        <v>0.797468354430379</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B44" s="5">
         <v>0.90909090909090895</v>
       </c>
-      <c r="C43" s="5">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C44" s="5">
+        <v>1</v>
+      </c>
+      <c r="D44" s="5">
         <v>0.952380952380952</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E44" s="5">
         <v>0.96456256921373196</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F44" s="5">
         <v>0.92920353982300796</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="I44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J44" s="5">
+        <v>0.90909090909090895</v>
+      </c>
+      <c r="K44" s="5">
+        <v>1</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0.952380952380952</v>
+      </c>
+      <c r="M44" s="5">
+        <v>0.96456256921373196</v>
+      </c>
+      <c r="N44" s="5">
+        <v>0.92920353982300796</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B45" s="5">
         <v>0.42857142857142799</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C45" s="5">
         <v>0.9</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D45" s="5">
         <v>0.58064516129032195</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E45" s="5">
         <v>0.72331227136680998</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F45" s="5">
         <v>0.46803069053708402</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="I45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="5">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="L45" s="5">
+        <v>0.58064516129032195</v>
+      </c>
+      <c r="M45" s="5">
+        <v>0.72331227136680998</v>
+      </c>
+      <c r="N45" s="5">
+        <v>0.46803069053708402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B46" s="5">
         <v>0.66948034233610498</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C46" s="5">
         <v>0.90959760379171395</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D46" s="5">
         <v>0.74500270274747005</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E46" s="5">
         <v>0.72359978113776302</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F46" s="5">
         <v>0.50491898743654295</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="I46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J46" s="5">
+        <v>0.670812901561054</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0.92148086230122195</v>
+      </c>
+      <c r="L46" s="5">
+        <v>0.749384490815728</v>
+      </c>
+      <c r="M46" s="5">
+        <v>0.73062662256726196</v>
+      </c>
+      <c r="N46" s="5">
+        <v>0.51955260613499199</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="I48" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="I49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B50" s="5">
         <v>0.94545454545454499</v>
       </c>
-      <c r="C49" s="5">
-        <v>1</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="C50" s="5">
+        <v>1</v>
+      </c>
+      <c r="D50" s="5">
         <v>0.97196261682242902</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E50" s="5">
         <v>0.91455273698264306</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F50" s="5">
         <v>0.82978723404255295</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="I50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="5">
+        <v>0.94545454545454499</v>
+      </c>
+      <c r="K50" s="5">
+        <v>1</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0.97196261682242902</v>
+      </c>
+      <c r="M50" s="5">
+        <v>0.91455273698264306</v>
+      </c>
+      <c r="N50" s="5">
+        <v>0.82978723404255295</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B51" s="5">
         <v>0.80952380952380898</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C51" s="5">
         <v>0.73913043478260798</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D51" s="5">
         <v>0.77272727272727204</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E51" s="5">
         <v>0.82683982683982604</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F51" s="5">
         <v>0.65405405405405403</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="I51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" s="5">
+        <v>0.80952380952380898</v>
+      </c>
+      <c r="K51" s="5">
+        <v>0.73913043478260798</v>
+      </c>
+      <c r="L51" s="5">
+        <v>0.77272727272727204</v>
+      </c>
+      <c r="M51" s="5">
+        <v>0.82683982683982604</v>
+      </c>
+      <c r="N51" s="5">
+        <v>0.65405405405405403</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B51" s="5">
-        <v>1</v>
-      </c>
-      <c r="C51" s="5">
+      <c r="B52" s="5">
+        <v>1</v>
+      </c>
+      <c r="C52" s="5">
         <v>0.31914893617021201</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D52" s="5">
         <v>0.483870967741935</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E52" s="5">
         <v>0.49951124144672499</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F52" s="5">
         <v>0.199374511336982</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="I52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J52" s="5">
+        <v>1</v>
+      </c>
+      <c r="K52" s="5">
+        <v>0.31914893617021201</v>
+      </c>
+      <c r="L52" s="5">
+        <v>0.483870967741935</v>
+      </c>
+      <c r="M52" s="5">
+        <v>0.49951124144672499</v>
+      </c>
+      <c r="N52" s="5">
+        <v>0.199374511336982</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B53" s="5">
         <v>0.91836734693877498</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C53" s="5">
         <v>0.95744680851063801</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D53" s="5">
         <v>0.9375</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E53" s="5">
         <v>0.875</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F53" s="5">
         <v>0.75032509752925802</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
+      <c r="I53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="5">
+        <v>0.91836734693877498</v>
+      </c>
+      <c r="K53" s="5">
+        <v>0.95744680851063801</v>
+      </c>
+      <c r="L53" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="M53" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="N53" s="5">
+        <v>0.75032509752925802</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B54" s="5">
         <v>0.65625</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C54" s="5">
         <v>0.95454545454545403</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D54" s="5">
         <v>0.77777777777777701</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E54" s="5">
         <v>0.80780780780780703</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F54" s="5">
         <v>0.625</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="I54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" s="5">
+        <v>0.65625</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0.95454545454545403</v>
+      </c>
+      <c r="L54" s="5">
+        <v>0.77777777777777701</v>
+      </c>
+      <c r="M54" s="5">
+        <v>0.80780780780780703</v>
+      </c>
+      <c r="N54" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B54" s="5">
-        <v>1</v>
-      </c>
-      <c r="C54" s="5">
+      <c r="B55" s="5">
+        <v>1</v>
+      </c>
+      <c r="C55" s="5">
         <v>0.84210526315789402</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D55" s="5">
         <v>0.91428571428571404</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E55" s="5">
         <v>0.76149068322981295</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F55" s="5">
         <v>0.53846153846153799</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
+      <c r="I55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J55" s="5">
+        <v>1</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0.84210526315789402</v>
+      </c>
+      <c r="L55" s="5">
+        <v>0.91428571428571404</v>
+      </c>
+      <c r="M55" s="5">
+        <v>0.76149068322981295</v>
+      </c>
+      <c r="N55" s="5">
+        <v>0.53846153846153799</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B56" s="5">
         <v>0.76744186046511598</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C56" s="5">
         <v>0.80487804878048697</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D56" s="5">
         <v>0.78571428571428503</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E56" s="5">
         <v>0.68831168831168799</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F56" s="5">
         <v>0.377297297297297</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
+      <c r="I56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" s="5">
+        <v>0.76744186046511598</v>
+      </c>
+      <c r="K56" s="5">
+        <v>0.80487804878048697</v>
+      </c>
+      <c r="L56" s="5">
+        <v>0.78571428571428503</v>
+      </c>
+      <c r="M56" s="5">
+        <v>0.68831168831168799</v>
+      </c>
+      <c r="N56" s="5">
+        <v>0.377297297297297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B57" s="5">
         <v>0.51923076923076905</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C57" s="5">
         <v>0.9</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D57" s="5">
         <v>0.65853658536585302</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E57" s="5">
         <v>0.52492046659597003</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F57" s="5">
         <v>0.157894736842105</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="I57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J57" s="5">
+        <v>0.51923076923076905</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0.65853658536585302</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0.52492046659597003</v>
+      </c>
+      <c r="N57" s="5">
+        <v>0.157894736842105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B58" s="5">
         <v>0.93023255813953398</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C58" s="5">
         <v>0.8</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D58" s="5">
         <v>0.86021505376343999</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E58" s="5">
         <v>0.74439324116743399</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F58" s="5">
         <v>0.49636803874092</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
+      <c r="I58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" s="5">
+        <v>0.93023255813953398</v>
+      </c>
+      <c r="K58" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="L58" s="5">
+        <v>0.86021505376343999</v>
+      </c>
+      <c r="M58" s="5">
+        <v>0.74439324116743399</v>
+      </c>
+      <c r="N58" s="5">
+        <v>0.49636803874092</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="5">
-        <v>1</v>
-      </c>
-      <c r="C58" s="5">
-        <v>1</v>
-      </c>
-      <c r="D58" s="5">
-        <v>1</v>
-      </c>
-      <c r="E58" s="5">
-        <v>1</v>
-      </c>
-      <c r="F58" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="B59" s="5">
+        <v>1</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5">
+        <v>1</v>
+      </c>
+      <c r="F59" s="5">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="5">
+        <v>0.97959183673469297</v>
+      </c>
+      <c r="K59" s="5">
+        <v>1</v>
+      </c>
+      <c r="L59" s="5">
+        <v>0.98969072164948402</v>
+      </c>
+      <c r="M59" s="5">
+        <v>0.97871632856667701</v>
+      </c>
+      <c r="N59" s="5">
+        <v>0.95744680851063801</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B59" s="5">
-        <v>1</v>
-      </c>
-      <c r="C59" s="5">
+      <c r="B60" s="5">
+        <v>1</v>
+      </c>
+      <c r="C60" s="5">
         <v>0.98039215686274495</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D60" s="5">
         <v>0.99009900990098998</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E60" s="5">
         <v>0.976530986431976</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F60" s="5">
         <v>0.95307917888562999</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="I60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J60" s="5">
+        <v>1</v>
+      </c>
+      <c r="K60" s="5">
+        <v>1</v>
+      </c>
+      <c r="L60" s="5">
+        <v>1</v>
+      </c>
+      <c r="M60" s="5">
+        <v>1</v>
+      </c>
+      <c r="N60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B61" s="5">
         <v>0.97727272727272696</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C61" s="5">
         <v>0.76785714285714202</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D61" s="5">
         <v>0.86</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E61" s="5">
         <v>0.67999999999999905</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F61" s="5">
         <v>0.39130434782608597</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+      <c r="I61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J61" s="5">
+        <v>0.97777777777777697</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0.78571428571428503</v>
+      </c>
+      <c r="L61" s="5">
+        <v>0.87128712871287095</v>
+      </c>
+      <c r="M61" s="5">
+        <v>0.694902823615694</v>
+      </c>
+      <c r="N61" s="5">
+        <v>0.41573033707865098</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B62" s="5">
         <v>0.98214285714285698</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C62" s="5">
         <v>0.98214285714285698</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D62" s="5">
         <v>0.98214285714285698</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E62" s="5">
         <v>0.92857142857142805</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F62" s="5">
         <v>0.85714285714285698</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="I62" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J62" s="5">
+        <v>0.98245614035087703</v>
+      </c>
+      <c r="K62" s="5">
+        <v>1</v>
+      </c>
+      <c r="L62" s="5">
+        <v>0.99115044247787598</v>
+      </c>
+      <c r="M62" s="5">
+        <v>0.96224188790560405</v>
+      </c>
+      <c r="N62" s="5">
+        <v>0.92452830188679203</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B63" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C63" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D63" s="5">
         <v>0.96363636363636296</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E63" s="5">
         <v>0.87070707070706999</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F63" s="5">
         <v>0.74141414141414097</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="I63" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J63" s="5">
+        <v>0.96428571428571397</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0.98181818181818103</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="M63" s="5">
+        <v>0.89825119236883899</v>
+      </c>
+      <c r="N63" s="5">
+        <v>0.79661016949152497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B64" s="5">
         <v>0.79661016949152497</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C64" s="5">
         <v>0.97916666666666596</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D64" s="5">
         <v>0.87850467289719603</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E64" s="5">
         <v>0.62972852692478798</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F64" s="5">
         <v>0.29729729729729698</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="I64" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="K64" s="5">
+        <v>1</v>
+      </c>
+      <c r="L64" s="5">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="M64" s="5">
+        <v>0.64444444444444404</v>
+      </c>
+      <c r="N64" s="5">
+        <v>0.33333333333333298</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B64" s="5">
-        <v>1</v>
-      </c>
-      <c r="C64" s="5">
+      <c r="B65" s="5">
+        <v>1</v>
+      </c>
+      <c r="C65" s="5">
         <v>0.93220338983050799</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D65" s="5">
         <v>0.96491228070175405</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E65" s="5">
         <v>0.83959899749373401</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F65" s="5">
         <v>0.682382133995037</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+      <c r="I65" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J65" s="5">
+        <v>1</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0.93220338983050799</v>
+      </c>
+      <c r="L65" s="5">
+        <v>0.96491228070175405</v>
+      </c>
+      <c r="M65" s="5">
+        <v>0.83959899749373401</v>
+      </c>
+      <c r="N65" s="5">
+        <v>0.682382133995037</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B66" s="5">
         <v>0.94736842105263097</v>
-      </c>
-      <c r="C65" s="5">
-        <v>0.94736842105263097</v>
-      </c>
-      <c r="D65" s="5">
-        <v>0.94736842105263097</v>
-      </c>
-      <c r="E65" s="5">
-        <v>0.96257309941520397</v>
-      </c>
-      <c r="F65" s="5">
-        <v>0.92514619883040905</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="5">
-        <v>0.81818181818181801</v>
       </c>
       <c r="C66" s="5">
         <v>0.94736842105263097</v>
       </c>
       <c r="D66" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0.96257309941520397</v>
+      </c>
+      <c r="F66" s="5">
+        <v>0.92514619883040905</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="K66" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="L66" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="M66" s="5">
+        <v>0.96257309941520397</v>
+      </c>
+      <c r="N66" s="5">
+        <v>0.92514619883040905</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="5">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="C67" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="D67" s="5">
         <v>0.87804878048780399</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E67" s="5">
         <v>0.91028875805999399</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F67" s="5">
         <v>0.82102908277404896</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+      <c r="I67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J67" s="5">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="L67" s="5">
+        <v>0.87804878048780399</v>
+      </c>
+      <c r="M67" s="5">
+        <v>0.91028875805999399</v>
+      </c>
+      <c r="N67" s="5">
+        <v>0.82102908277404896</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B68" s="5">
         <v>0.80952380952380898</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C68" s="5">
         <v>0.94444444444444398</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D68" s="5">
         <v>0.87179487179487103</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E68" s="5">
         <v>0.90780754825698595</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F68" s="5">
         <v>0.81609195402298795</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="I68" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="5">
+        <v>0.80952380952380898</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0.94444444444444398</v>
+      </c>
+      <c r="L68" s="5">
+        <v>0.87179487179487103</v>
+      </c>
+      <c r="M68" s="5">
+        <v>0.90780754825698595</v>
+      </c>
+      <c r="N68" s="5">
+        <v>0.81609195402298795</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B69" s="5">
         <v>0.88638089768706696</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C69" s="5">
         <v>0.88220183207859404</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D69" s="5">
         <v>0.86837355430595597</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E69" s="5">
         <v>0.80782284780226798</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F69" s="5">
         <v>0.63754998423648401</v>
       </c>
+      <c r="I69" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J69" s="5">
+        <v>0.88556244250841398</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0.88716695209789298</v>
+      </c>
+      <c r="L69" s="5">
+        <v>0.87045814647041397</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0.812718566974162</v>
+      </c>
+      <c r="N69" s="5">
+        <v>0.64741372780147999</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="8">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="I25:N25"/>
+    <mergeCell ref="I48:N48"/>
   </mergeCells>
-  <conditionalFormatting sqref="B1:F1048576">
+  <conditionalFormatting sqref="B2:F1048576">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:N2">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:N69">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3350,24 +5645,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="F1" s="12" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="I1" s="11" t="s">
+      <c r="G1" s="14"/>
+      <c r="I1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="L1" s="11" t="s">
+      <c r="J1" s="13"/>
+      <c r="L1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="11"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3405,7 +5700,7 @@
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>0.94074074074073999</v>
       </c>
       <c r="C3" s="7">
@@ -3439,7 +5734,7 @@
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>0.60816326530612197</v>
       </c>
       <c r="C4" s="7">
@@ -3473,7 +5768,7 @@
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>0.81626794258373203</v>
       </c>
       <c r="C5" s="7">
@@ -3507,7 +5802,7 @@
       <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>0.85029239766081799</v>
       </c>
       <c r="C6" s="7">
@@ -3541,7 +5836,7 @@
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>0.90588235294117603</v>
       </c>
       <c r="C7" s="7">
@@ -3575,7 +5870,7 @@
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>0.79937304075235105</v>
       </c>
       <c r="C8" s="7">
@@ -3609,7 +5904,7 @@
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.75969962453066298</v>
       </c>
       <c r="C9" s="7">
@@ -3643,7 +5938,7 @@
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>0.94871794871794801</v>
       </c>
       <c r="C10" s="7">
@@ -3677,7 +5972,7 @@
       <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.68058838980824699</v>
       </c>
       <c r="C11" s="7">
@@ -3711,16 +6006,16 @@
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="7">
-        <v>0.97871632856667701</v>
+      <c r="B12" s="5">
+        <v>1</v>
       </c>
       <c r="C12" s="7">
         <f t="shared" si="0"/>
-        <v>-2.1283671433322993E-2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1283671433322993E-2</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>34</v>
@@ -3745,16 +6040,16 @@
       <c r="A13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="7">
-        <v>0.976530986431976</v>
+      <c r="B13" s="5">
+        <v>1</v>
       </c>
       <c r="C13" s="7">
         <f t="shared" si="0"/>
-        <v>-2.3469013568024E-2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="7">
         <f t="shared" si="1"/>
-        <v>-2.3469013568024E-2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>35</v>
@@ -3779,16 +6074,16 @@
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="7">
-        <v>0.60464541635779501</v>
+      <c r="B14" s="5">
+        <v>0.61904761904761896</v>
       </c>
       <c r="C14" s="7">
         <f t="shared" si="0"/>
-        <v>5.6872758907719034E-2</v>
+        <v>7.1274961597542985E-2</v>
       </c>
       <c r="D14" s="7">
         <f t="shared" si="1"/>
-        <v>0.10156643376074104</v>
+        <v>0.11596863645056499</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>36</v>
@@ -3813,16 +6108,16 @@
       <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="7">
-        <v>0.96224188790560405</v>
+      <c r="B15" s="5">
+        <v>1</v>
       </c>
       <c r="C15" s="7">
         <f t="shared" si="0"/>
-        <v>6.3990695536765063E-2</v>
+        <v>0.10174880763116101</v>
       </c>
       <c r="D15" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.7758112094395946E-2</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>37</v>
@@ -3847,16 +6142,16 @@
       <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="7">
-        <v>0.87070707070706999</v>
+      <c r="B16" s="5">
+        <v>0.89825119236883899</v>
       </c>
       <c r="C16" s="7">
         <f t="shared" si="0"/>
-        <v>-9.5376660082542974E-2</v>
+        <v>-6.7832538420773969E-2</v>
       </c>
       <c r="D16" s="7">
         <f t="shared" si="1"/>
-        <v>-6.4646464646465063E-2</v>
+        <v>-3.7102342984696057E-2</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>38</v>
@@ -3881,16 +6176,16 @@
       <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="7">
-        <v>0.71428571428571397</v>
+      <c r="B17" s="5">
+        <v>0.73569321533923304</v>
       </c>
       <c r="C17" s="7">
         <f t="shared" si="0"/>
-        <v>3.4686214911496926E-2</v>
+        <v>5.6093715965016E-2</v>
       </c>
       <c r="D17" s="7">
         <f t="shared" si="1"/>
-        <v>-2.755513646602703E-2</v>
+        <v>-6.1476354125079569E-3</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>39</v>
@@ -3915,7 +6210,7 @@
       <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>0.65170068027210803</v>
       </c>
       <c r="C18" s="7">
@@ -3949,7 +6244,7 @@
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>0.98099198099198104</v>
       </c>
       <c r="C19" s="7">
@@ -3983,7 +6278,7 @@
       <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>0.92727272727272703</v>
       </c>
       <c r="C20" s="7">
@@ -4017,7 +6312,7 @@
       <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>0.90495990495990497</v>
       </c>
       <c r="C21" s="7">
@@ -4052,12 +6347,12 @@
       <c r="D22"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -4077,7 +6372,7 @@
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="5">
         <v>0.70833333333333304</v>
       </c>
       <c r="C25" s="7">
@@ -4093,7 +6388,7 @@
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="5">
         <v>0.79220779220779203</v>
       </c>
       <c r="C26" s="7">
@@ -4109,7 +6404,7 @@
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="5">
         <v>0.71964956195244001</v>
       </c>
       <c r="C27" s="7">
@@ -4125,7 +6420,7 @@
       <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="5">
         <v>0.34117647058823503</v>
       </c>
       <c r="C28" s="7">
@@ -4141,7 +6436,7 @@
       <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <v>0.75553857906799005</v>
       </c>
       <c r="C29" s="7">
@@ -4157,7 +6452,7 @@
       <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="5">
         <v>0.65280289330922203</v>
       </c>
       <c r="C30" s="7">
@@ -4173,7 +6468,7 @@
       <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="5">
         <v>0.606976172930483</v>
       </c>
       <c r="C31" s="7">
@@ -4189,7 +6484,7 @@
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="5">
         <v>0.69498177740398004</v>
       </c>
       <c r="C32" s="7">
@@ -4205,7 +6500,7 @@
       <c r="A33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="5">
         <v>0.63841807909604498</v>
       </c>
       <c r="C33" s="7">
@@ -4221,103 +6516,103 @@
       <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="7">
-        <v>0.97871632856667701</v>
+      <c r="B34" s="5">
+        <v>1</v>
       </c>
       <c r="C34" s="7">
         <f t="shared" si="2"/>
-        <v>-2.1283671433322993E-2</v>
+        <v>0</v>
       </c>
       <c r="D34" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.1283671433322993E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="7">
-        <v>0.976530986431976</v>
+      <c r="B35" s="5">
+        <v>1</v>
       </c>
       <c r="C35" s="7">
         <f t="shared" si="2"/>
-        <v>-2.3469013568024E-2</v>
+        <v>0</v>
       </c>
       <c r="D35" s="7">
         <f t="shared" si="3"/>
-        <v>-2.3469013568024E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="7">
-        <v>0.38461538461538403</v>
+      <c r="B36" s="5">
+        <v>0.40427672955974803</v>
       </c>
       <c r="C36" s="7">
         <f t="shared" si="2"/>
-        <v>-0.16315727283469195</v>
+        <v>-0.14349592789032795</v>
       </c>
       <c r="D36" s="7">
         <f t="shared" si="3"/>
-        <v>0.13461538461538403</v>
+        <v>0.15427672955974803</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="7">
-        <v>0.87070707070706999</v>
+      <c r="B37" s="5">
+        <v>0.89825119236883899</v>
       </c>
       <c r="C37" s="7">
         <f t="shared" si="2"/>
-        <v>-2.7544121661769005E-2</v>
+        <v>0</v>
       </c>
       <c r="D37" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.7544121661769005E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="7">
-        <v>0.89825119236883899</v>
+      <c r="B38" s="5">
+        <v>0.92857142857142805</v>
       </c>
       <c r="C38" s="7">
         <f t="shared" si="2"/>
-        <v>-6.7832538420773969E-2</v>
+        <v>-3.7512302218184912E-2</v>
       </c>
       <c r="D38" s="7">
         <f t="shared" si="3"/>
-        <v>-6.7832538420773969E-2</v>
+        <v>-3.7512302218184912E-2</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="7">
-        <v>0.54285714285714204</v>
+      <c r="B39" s="5">
+        <v>0.554088742207554</v>
       </c>
       <c r="C39" s="7">
         <f t="shared" si="2"/>
-        <v>-0.136742356517075</v>
+        <v>-0.12551075716666305</v>
       </c>
       <c r="D39" s="7">
         <f t="shared" si="3"/>
-        <v>-0.21744248261102195</v>
+        <v>-0.20621088326060999</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>0.60083160083160003</v>
       </c>
       <c r="C40" s="7">
@@ -4333,7 +6628,7 @@
       <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="5">
         <v>0.89792663476874002</v>
       </c>
       <c r="C41" s="7">
@@ -4349,7 +6644,7 @@
       <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="5">
         <v>0.96456256921373196</v>
       </c>
       <c r="C42" s="7">
@@ -4365,7 +6660,7 @@
       <c r="A43" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="5">
         <v>0.72331227136680998</v>
       </c>
       <c r="C43" s="7">
@@ -4382,12 +6677,12 @@
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -4407,7 +6702,7 @@
       <c r="A47" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="5">
         <v>0.91455273698264306</v>
       </c>
       <c r="C47" s="7">
@@ -4423,7 +6718,7 @@
       <c r="A48" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="5">
         <v>0.82683982683982604</v>
       </c>
       <c r="C48" s="7">
@@ -4439,7 +6734,7 @@
       <c r="A49" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="5">
         <v>0.49951124144672499</v>
       </c>
       <c r="C49" s="7">
@@ -4455,7 +6750,7 @@
       <c r="A50" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="5">
         <v>0.875</v>
       </c>
       <c r="C50" s="7">
@@ -4471,7 +6766,7 @@
       <c r="A51" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="5">
         <v>0.80780780780780703</v>
       </c>
       <c r="C51" s="7">
@@ -4487,7 +6782,7 @@
       <c r="A52" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="5">
         <v>0.76149068322981295</v>
       </c>
       <c r="C52" s="7">
@@ -4503,7 +6798,7 @@
       <c r="A53" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="5">
         <v>0.68831168831168799</v>
       </c>
       <c r="C53" s="7">
@@ -4519,7 +6814,7 @@
       <c r="A54" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="5">
         <v>0.52492046659597003</v>
       </c>
       <c r="C54" s="7">
@@ -4535,7 +6830,7 @@
       <c r="A55" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="5">
         <v>0.74439324116743399</v>
       </c>
       <c r="C55" s="7">
@@ -4551,103 +6846,103 @@
       <c r="A56" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="7">
-        <v>1</v>
+      <c r="B56" s="5">
+        <v>0.97871632856667701</v>
       </c>
       <c r="C56" s="7">
         <f t="shared" si="4"/>
-        <v>2.1283671433322993E-2</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.1283671433322993E-2</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="7">
-        <v>0.976530986431976</v>
+      <c r="B57" s="5">
+        <v>1</v>
       </c>
       <c r="C57" s="7">
         <f t="shared" si="4"/>
-        <v>-2.3469013568024E-2</v>
+        <v>0</v>
       </c>
       <c r="D57" s="7">
         <f t="shared" si="5"/>
-        <v>-2.3469013568024E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="7">
-        <v>0.67999999999999905</v>
+      <c r="B58" s="5">
+        <v>0.694902823615694</v>
       </c>
       <c r="C58" s="7">
         <f t="shared" si="4"/>
-        <v>0.17692101740294508</v>
+        <v>0.19182384101864003</v>
       </c>
       <c r="D58" s="7">
         <f t="shared" si="5"/>
-        <v>0.35464541635779501</v>
+        <v>0.36904761904761896</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="7">
-        <v>0.92857142857142805</v>
+      <c r="B59" s="5">
+        <v>0.96224188790560405</v>
       </c>
       <c r="C59" s="7">
         <f t="shared" si="4"/>
-        <v>-3.3670459334176006E-2</v>
+        <v>0</v>
       </c>
       <c r="D59" s="7">
         <f t="shared" si="5"/>
-        <v>9.1534817198534069E-2</v>
+        <v>0.12929292929293001</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="7">
-        <v>0.87070707070706999</v>
+      <c r="B60" s="5">
+        <v>0.89825119236883899</v>
       </c>
       <c r="C60" s="7">
         <f t="shared" si="4"/>
-        <v>-6.4646464646465063E-2</v>
+        <v>-3.7102342984696057E-2</v>
       </c>
       <c r="D60" s="7">
         <f t="shared" si="5"/>
-        <v>-9.5376660082542974E-2</v>
+        <v>-6.7832538420773969E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B61" s="7">
-        <v>0.62972852692478798</v>
+      <c r="B61" s="5">
+        <v>0.64444444444444404</v>
       </c>
       <c r="C61" s="7">
         <f t="shared" si="4"/>
-        <v>-0.11211232382695302</v>
+        <v>-9.7396406307296957E-2</v>
       </c>
       <c r="D61" s="7">
         <f t="shared" si="5"/>
-        <v>-4.6013911182450018E-2</v>
+        <v>-2.4606410128930944E-2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="5">
         <v>0.83959899749373401</v>
       </c>
       <c r="C62" s="7">
@@ -4663,7 +6958,7 @@
       <c r="A63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="5">
         <v>0.96257309941520397</v>
       </c>
       <c r="C63" s="7">
@@ -4679,7 +6974,7 @@
       <c r="A64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="5">
         <v>0.91028875805999399</v>
       </c>
       <c r="C64" s="7">
@@ -4695,7 +6990,7 @@
       <c r="A65" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="5">
         <v>0.90780754825698595</v>
       </c>
       <c r="C65" s="7">
@@ -4717,7 +7012,7 @@
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:A21 H1:I1 K1:L1 G23:M1048576 G2:M21">
-    <cfRule type="colorScale" priority="40">
+    <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4729,7 +7024,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A43">
-    <cfRule type="colorScale" priority="39">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4741,7 +7036,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:A65">
-    <cfRule type="colorScale" priority="38">
+    <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4753,18 +7048,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:D1 C3:D21 C23:D23 C25:D43 C45:D45 C47:D65 C1591:D1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F21">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4774,7 +7069,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="54">
+    <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4784,7 +7079,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="55">
+    <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4796,7 +7091,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G21">
-    <cfRule type="colorScale" priority="81">
+    <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4806,7 +7101,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="82">
+    <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4816,7 +7111,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="83">
+    <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4828,6 +7123,70 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I21">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J21">
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="93">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L21">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4859,8 +7218,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J21">
-    <cfRule type="colorScale" priority="88">
+  <conditionalFormatting sqref="M2:M21">
+    <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4870,7 +7229,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="89">
+    <cfRule type="colorScale" priority="95">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4880,7 +7239,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="90">
+    <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4891,8 +7250,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
-    <cfRule type="colorScale" priority="17">
+  <conditionalFormatting sqref="B3:B21">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4902,29 +7261,9 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
-    <cfRule type="colorScale" priority="91">
+  <conditionalFormatting sqref="B25:B43">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -4934,21 +7273,13 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="92">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B65">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>

--- a/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
+++ b/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\initial_testing_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81240C69-8B45-404A-A16A-13B6E294F9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D8FAB5-BC70-4C52-A0D0-653DA824C05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="4" r:id="rId1"/>
@@ -211,7 +211,7 @@
     <t>Using JSON-repair</t>
   </si>
   <si>
-    <t>JSON-repair (only one response for TASKS was previously unparsable)</t>
+    <t>JSON-repair (only one response for TASKS was previously unparsable - difference is visible in questions from Outlook to Relevance)</t>
   </si>
 </sst>
 </file>
@@ -309,12 +309,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -324,7 +318,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -658,40 +658,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="J1" s="15" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="J1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="J2" s="10" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="J2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
@@ -1464,22 +1464,22 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="J24" s="10" t="s">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="J24" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
@@ -2252,22 +2252,22 @@
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="J46" s="10" t="s">
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="J46" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -3096,19 +3096,19 @@
     <col min="11" max="11" width="20.140625" style="5" customWidth="1"/>
     <col min="12" max="12" width="19" style="5" customWidth="1"/>
     <col min="13" max="13" width="17.28515625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="15" style="5" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" style="5" customWidth="1"/>
     <col min="15" max="15" width="15.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
       <c r="I1" s="16" t="s">
         <v>57</v>
       </c>
@@ -3119,22 +3119,22 @@
       <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="I2" s="11" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="I2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -3940,22 +3940,22 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="I25" s="11" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="I25" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -4759,22 +4759,22 @@
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="I48" s="11" t="s">
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="I48" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
@@ -5645,24 +5645,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="F1" s="14" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="I1" s="13" t="s">
+      <c r="G1" s="12"/>
+      <c r="I1" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="L1" s="13" t="s">
+      <c r="J1" s="11"/>
+      <c r="L1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="13"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -6347,12 +6347,12 @@
       <c r="D22"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -6677,12 +6677,12 @@
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -7037,6 +7037,42 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A46:A65">
     <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B21">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25:B43">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B65">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -7250,42 +7286,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B43">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B65">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
+++ b/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\initial_testing_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D8FAB5-BC70-4C52-A0D0-653DA824C05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CE421D-88E4-4621-BE96-9E4B7364C077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="62">
   <si>
     <t>Model</t>
   </si>
@@ -213,6 +213,18 @@
   <si>
     <t>JSON-repair (only one response for TASKS was previously unparsable - difference is visible in questions from Outlook to Relevance)</t>
   </si>
+  <si>
+    <t>human1</t>
+  </si>
+  <si>
+    <t>human2</t>
+  </si>
+  <si>
+    <t>human3</t>
+  </si>
+  <si>
+    <t>F1 makro mēra vērtības</t>
+  </si>
 </sst>
 </file>
 
@@ -309,15 +321,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -328,6 +331,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -641,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F8CBD-665F-4514-96E7-546603B512CB}">
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" customWidth="1"/>
@@ -655,45 +667,55 @@
     <col min="12" max="12" width="18" style="5" customWidth="1"/>
     <col min="13" max="13" width="17.28515625" style="5" customWidth="1"/>
     <col min="14" max="15" width="13.42578125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="23.5703125" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="21" max="21" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="J1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="J2" s="13" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="J2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="R2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
@@ -730,8 +752,18 @@
       <c r="O3" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R3" s="8"/>
+      <c r="S3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
@@ -768,8 +800,20 @@
       <c r="O4" s="5">
         <v>0.56790237588980297</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4" s="7">
+        <v>0.78304612706701404</v>
+      </c>
+      <c r="T4" s="7">
+        <v>0.69719032642402901</v>
+      </c>
+      <c r="U4" s="7">
+        <v>0.76954108569107804</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
@@ -806,8 +850,20 @@
       <c r="O5" s="5">
         <v>0.60388492181939202</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" s="7">
+        <v>0.80147966804919502</v>
+      </c>
+      <c r="T5" s="7">
+        <v>0.69586147114953001</v>
+      </c>
+      <c r="U5" s="7">
+        <v>0.76385134456426296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
@@ -844,8 +900,20 @@
       <c r="O6" s="5">
         <v>0.59943659412058703</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0.79962213225371104</v>
+      </c>
+      <c r="T6" s="7">
+        <v>0.69496220838286704</v>
+      </c>
+      <c r="U6" s="7">
+        <v>0.75782567947516399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
@@ -882,8 +950,20 @@
       <c r="O7" s="5">
         <v>0.67138435366112903</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="S7" s="7">
+        <v>0.83331423242435398</v>
+      </c>
+      <c r="T7" s="7">
+        <v>0.69978773477687595</v>
+      </c>
+      <c r="U7" s="7">
+        <v>0.81241841580824603</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
@@ -920,8 +1000,20 @@
       <c r="O8" s="5">
         <v>0.320677619817825</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0.65352176886254798</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0.62954963972810196</v>
+      </c>
+      <c r="U8" s="7">
+        <v>0.61177628027174302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
@@ -958,8 +1050,20 @@
       <c r="O9" s="5">
         <v>0.35685204527529601</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0.67233886299511203</v>
+      </c>
+      <c r="T9" s="7">
+        <v>0.64547165310503796</v>
+      </c>
+      <c r="U9" s="7">
+        <v>0.63058194069840501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
@@ -996,8 +1100,20 @@
       <c r="O10" s="5">
         <v>0.45795544598045201</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0.72811288880055602</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0.68087875221514205</v>
+      </c>
+      <c r="U10" s="7">
+        <v>0.715714193164949</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
@@ -1034,8 +1150,20 @@
       <c r="O11" s="5">
         <v>0.59666144530428</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="7">
+        <v>0.79656485033404401</v>
+      </c>
+      <c r="T11" s="7">
+        <v>0.69898798689479402</v>
+      </c>
+      <c r="U11" s="7">
+        <v>0.80123628745409903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>9</v>
       </c>
@@ -1072,8 +1200,20 @@
       <c r="O12" s="5">
         <v>0.53764768118497597</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="7">
+        <v>0.76816976127320902</v>
+      </c>
+      <c r="T12" s="7">
+        <v>0.72033345689601502</v>
+      </c>
+      <c r="U12" s="7">
+        <v>0.73075718899403397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>10</v>
       </c>
@@ -1110,8 +1250,20 @@
       <c r="O13" s="5">
         <v>0.57895655208515096</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" s="7">
+        <v>0.78814749780509197</v>
+      </c>
+      <c r="T13" s="7">
+        <v>0.73022739877981102</v>
+      </c>
+      <c r="U13" s="7">
+        <v>0.72333933531538297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -1148,8 +1300,20 @@
       <c r="O14" s="5">
         <v>0.60225374696568101</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="S14" s="7">
+        <v>0.80097603647286797</v>
+      </c>
+      <c r="T14" s="7">
+        <v>0.71417404174752996</v>
+      </c>
+      <c r="U14" s="7">
+        <v>0.75626690976063604</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -1186,8 +1350,20 @@
       <c r="O15" s="5">
         <v>0.58985040711986303</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="S15" s="7">
+        <v>0.79173076923076902</v>
+      </c>
+      <c r="T15" s="7">
+        <v>0.68994802392860599</v>
+      </c>
+      <c r="U15" s="7">
+        <v>0.80506388797208694</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>13</v>
       </c>
@@ -1224,8 +1400,20 @@
       <c r="O16" s="5">
         <v>0.67202557967935905</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="7">
+        <v>0.83596224212707804</v>
+      </c>
+      <c r="T16" s="6">
+        <v>0.77657591690481198</v>
+      </c>
+      <c r="U16" s="7">
+        <v>0.78122833990975704</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>14</v>
       </c>
@@ -1262,8 +1450,20 @@
       <c r="O17" s="5">
         <v>0.36403791090493398</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="S17" s="7">
+        <v>0.68161061557234903</v>
+      </c>
+      <c r="T17" s="7">
+        <v>0.63860852257918199</v>
+      </c>
+      <c r="U17" s="7">
+        <v>0.68117484636203596</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
@@ -1300,8 +1500,20 @@
       <c r="O18" s="5">
         <v>0.57960726468147805</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0.789101252211315</v>
+      </c>
+      <c r="T18" s="7">
+        <v>0.69436241721353997</v>
+      </c>
+      <c r="U18" s="7">
+        <v>0.77605759066667002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>51</v>
       </c>
@@ -1338,8 +1550,20 @@
       <c r="O19" s="5">
         <v>0.67550826272592501</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="S19" s="7">
+        <v>0.83743844753052399</v>
+      </c>
+      <c r="T19" s="7">
+        <v>0.76055460257203999</v>
+      </c>
+      <c r="U19" s="7">
+        <v>0.79254244103278504</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>52</v>
       </c>
@@ -1376,8 +1600,20 @@
       <c r="O20" s="4">
         <v>0.74627587318398403</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="S20" s="6">
+        <v>0.87275111483504597</v>
+      </c>
+      <c r="T20" s="7">
+        <v>0.76214905902143104</v>
+      </c>
+      <c r="U20" s="6">
+        <v>0.83914274034009595</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>53</v>
       </c>
@@ -1414,8 +1650,20 @@
       <c r="O21" s="5">
         <v>0.50695386702849299</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="S21" s="7">
+        <v>0.74782042940793703</v>
+      </c>
+      <c r="T21" s="7">
+        <v>0.71841346035966502</v>
+      </c>
+      <c r="U21" s="7">
+        <v>0.68078316629978497</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>54</v>
       </c>
@@ -1463,25 +1711,25 @@
         <v>0.74627587318398403</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="J24" s="13" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="J24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1805,7 @@
         <v>0.41636436920596498</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>2</v>
       </c>
@@ -1595,7 +1843,7 @@
         <v>0.41039878849066103</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>3</v>
       </c>
@@ -1633,7 +1881,7 @@
         <v>0.40368644926068398</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>4</v>
       </c>
@@ -1671,7 +1919,7 @@
         <v>0.43446480424551898</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>5</v>
       </c>
@@ -1709,7 +1957,7 @@
         <v>0.25919801570897</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>6</v>
       </c>
@@ -1747,7 +1995,7 @@
         <v>0.290982336535481</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>7</v>
       </c>
@@ -2252,22 +2500,22 @@
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="J46" s="13" t="s">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="J46" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
@@ -3040,7 +3288,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="R2:U2"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A46:F46"/>
@@ -3051,7 +3300,7 @@
     <mergeCell ref="J1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:F1048576">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3063,7 +3312,55 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:O66">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S4:S21">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S1:U1048576">
     <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T4:T21">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U4:U21">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3101,40 +3398,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="I1" s="16" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="I1" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="I2" s="15" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="I2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -3940,22 +4237,22 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="I25" s="15" t="s">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -4759,22 +5056,22 @@
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="I48" s="15" t="s">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="I48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
@@ -5645,24 +5942,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="F1" s="12" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="F1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="I1" s="11" t="s">
+      <c r="G1" s="16"/>
+      <c r="I1" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="L1" s="11" t="s">
+      <c r="J1" s="15"/>
+      <c r="L1" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="11"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -6347,12 +6644,12 @@
       <c r="D22"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -6677,12 +6974,12 @@
       <c r="D44"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">

--- a/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
+++ b/src/results/llm/initial_testing_01/results_for_presentation_initial_testing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\initial_testing_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CE421D-88E4-4621-BE96-9E4B7364C077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B15DE9-6CF5-4731-917E-CF1775367449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="4" r:id="rId1"/>
@@ -230,7 +230,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,13 +254,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -307,10 +319,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -342,8 +355,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Accent5" xfId="1" builtinId="45"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -5924,7 +5939,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1170AC05-0E05-482F-8AFE-200C8B605317}">
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -5937,17 +5952,13 @@
     <col min="8" max="8" width="15.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" style="5" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" style="5" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="5"/>
-    <col min="13" max="13" width="12.42578125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12" style="5" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+    <row r="1" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F1" s="16" t="s">
         <v>45</v>
       </c>
@@ -5961,19 +5972,7 @@
       </c>
       <c r="M1" s="15"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>49</v>
-      </c>
+    <row r="2" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F2" s="3" t="s">
         <v>24</v>
       </c>
@@ -5993,21 +5992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.94074074074073999</v>
-      </c>
-      <c r="C3" s="7">
-        <f>B3-G3</f>
-        <v>0.22109117878829998</v>
-      </c>
-      <c r="D3" s="7">
-        <f>B3-M3</f>
-        <v>7.3245916724177018E-2</v>
-      </c>
+    <row r="3" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
@@ -6027,21 +6012,7 @@
         <v>0.86749482401656297</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="5">
-        <v>0.60816326530612197</v>
-      </c>
-      <c r="C4" s="7">
-        <f t="shared" ref="C4:C21" si="0">B4-G4</f>
-        <v>-1.683673469387803E-2</v>
-      </c>
-      <c r="D4" s="7">
-        <f t="shared" ref="D4:D21" si="1">B4-M4</f>
-        <v>2.4829931972788932E-2</v>
-      </c>
+    <row r="4" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F4" s="3" t="s">
         <v>26</v>
       </c>
@@ -6061,21 +6032,7 @@
         <v>0.58333333333333304</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.81626794258373203</v>
-      </c>
-      <c r="C5" s="7">
-        <f t="shared" si="0"/>
-        <v>0.10138822770401801</v>
-      </c>
-      <c r="D5" s="7">
-        <f t="shared" si="1"/>
-        <v>0.30076122707701702</v>
-      </c>
+    <row r="5" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
@@ -6095,21 +6052,7 @@
         <v>0.51550671550671501</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.85029239766081799</v>
-      </c>
-      <c r="C6" s="7">
-        <f t="shared" si="0"/>
-        <v>0.40089968511021101</v>
-      </c>
-      <c r="D6" s="7">
-        <f t="shared" si="1"/>
-        <v>-4.2530568846360639E-3</v>
-      </c>
+    <row r="6" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F6" s="3" t="s">
         <v>28</v>
       </c>
@@ -6129,21 +6072,7 @@
         <v>0.85454545454545405</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.90588235294117603</v>
-      </c>
-      <c r="C7" s="7">
-        <f t="shared" si="0"/>
-        <v>5.7182589347796076E-2</v>
-      </c>
-      <c r="D7" s="7">
-        <f t="shared" si="1"/>
-        <v>3.7164404223227976E-2</v>
-      </c>
+    <row r="7" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F7" s="3" t="s">
         <v>29</v>
       </c>
@@ -6163,21 +6092,7 @@
         <v>0.86871794871794805</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.79937304075235105</v>
-      </c>
-      <c r="C8" s="7">
-        <f t="shared" si="0"/>
-        <v>0.17264981699837501</v>
-      </c>
-      <c r="D8" s="7">
-        <f t="shared" si="1"/>
-        <v>-2.2849181469870916E-2</v>
-      </c>
+    <row r="8" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F8" s="3" t="s">
         <v>30</v>
       </c>
@@ -6197,21 +6112,7 @@
         <v>0.82222222222222197</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.75969962453066298</v>
-      </c>
-      <c r="C9" s="7">
-        <f t="shared" si="0"/>
-        <v>0.26491989445681596</v>
-      </c>
-      <c r="D9" s="7">
-        <f t="shared" si="1"/>
-        <v>-8.4163174983220568E-3</v>
-      </c>
+    <row r="9" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F9" s="3" t="s">
         <v>31</v>
       </c>
@@ -6231,21 +6132,7 @@
         <v>0.76811594202898503</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="5">
-        <v>0.94871794871794801</v>
-      </c>
-      <c r="C10" s="7">
-        <f t="shared" si="0"/>
-        <v>0.25373617131396797</v>
-      </c>
-      <c r="D10" s="7">
-        <f t="shared" si="1"/>
-        <v>0.38986322973597598</v>
-      </c>
+    <row r="10" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F10" s="3" t="s">
         <v>32</v>
       </c>
@@ -6265,21 +6152,7 @@
         <v>0.55885471898197203</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.68058838980824699</v>
-      </c>
-      <c r="C11" s="7">
-        <f t="shared" si="0"/>
-        <v>2.4338389808246985E-2</v>
-      </c>
-      <c r="D11" s="7">
-        <f t="shared" si="1"/>
-        <v>7.861117080975033E-3</v>
-      </c>
+    <row r="11" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F11" s="3" t="s">
         <v>33</v>
       </c>
@@ -6299,21 +6172,7 @@
         <v>0.67272727272727195</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <f t="shared" si="1"/>
-        <v>2.1283671433322993E-2</v>
-      </c>
+    <row r="12" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F12" s="3" t="s">
         <v>34</v>
       </c>
@@ -6333,21 +6192,7 @@
         <v>0.97871632856667701</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D13" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="13" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F13" s="3" t="s">
         <v>35</v>
       </c>
@@ -6367,21 +6212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0.61904761904761896</v>
-      </c>
-      <c r="C14" s="7">
-        <f t="shared" si="0"/>
-        <v>7.1274961597542985E-2</v>
-      </c>
-      <c r="D14" s="7">
-        <f t="shared" si="1"/>
-        <v>0.11596863645056499</v>
-      </c>
+    <row r="14" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F14" s="3" t="s">
         <v>36</v>
       </c>
@@ -6401,21 +6232,7 @@
         <v>0.50307898259705397</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="7">
-        <f t="shared" si="0"/>
-        <v>0.10174880763116101</v>
-      </c>
-      <c r="D15" s="7">
-        <f t="shared" si="1"/>
-        <v>3.7758112094395946E-2</v>
-      </c>
+    <row r="15" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F15" s="3" t="s">
         <v>37</v>
       </c>
@@ -6435,21 +6252,7 @@
         <v>0.96224188790560405</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5">
-        <v>0.89825119236883899</v>
-      </c>
-      <c r="C16" s="7">
-        <f t="shared" si="0"/>
-        <v>-6.7832538420773969E-2</v>
-      </c>
-      <c r="D16" s="7">
-        <f t="shared" si="1"/>
-        <v>-3.7102342984696057E-2</v>
-      </c>
+    <row r="16" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F16" s="3" t="s">
         <v>38</v>
       </c>
@@ -6469,21 +6272,7 @@
         <v>0.93535353535353505</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5">
-        <v>0.73569321533923304</v>
-      </c>
-      <c r="C17" s="7">
-        <f t="shared" si="0"/>
-        <v>5.6093715965016E-2</v>
-      </c>
-      <c r="D17" s="7">
-        <f t="shared" si="1"/>
-        <v>-6.1476354125079569E-3</v>
-      </c>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F17" s="3" t="s">
         <v>39</v>
       </c>
@@ -6503,21 +6292,7 @@
         <v>0.741840850751741</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0.65170068027210803</v>
-      </c>
-      <c r="C18" s="7">
-        <f t="shared" si="0"/>
-        <v>3.1964178076293037E-2</v>
-      </c>
-      <c r="D18" s="7">
-        <f t="shared" si="1"/>
-        <v>3.7824360513436073E-2</v>
-      </c>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F18" s="3" t="s">
         <v>40</v>
       </c>
@@ -6537,21 +6312,7 @@
         <v>0.61387631975867196</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0.98099198099198104</v>
-      </c>
-      <c r="C19" s="7">
-        <f t="shared" si="0"/>
-        <v>6.4325314325315075E-2</v>
-      </c>
-      <c r="D19" s="7">
-        <f t="shared" si="1"/>
-        <v>3.8016038016038034E-2</v>
-      </c>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F19" s="3" t="s">
         <v>41</v>
       </c>
@@ -6571,21 +6332,7 @@
         <v>0.942975942975943</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5">
-        <v>0.92727272727272703</v>
-      </c>
-      <c r="C20" s="7">
-        <f t="shared" si="0"/>
-        <v>-3.5300372142476943E-2</v>
-      </c>
-      <c r="D20" s="7">
-        <f t="shared" si="1"/>
-        <v>-1.5703215703215978E-2</v>
-      </c>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F20" s="3" t="s">
         <v>42</v>
       </c>
@@ -6605,21 +6352,7 @@
         <v>0.942975942975943</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="5">
-        <v>0.90495990495990497</v>
-      </c>
-      <c r="C21" s="7">
-        <f t="shared" si="0"/>
-        <v>0.14628720511073501</v>
-      </c>
-      <c r="D21" s="7">
-        <f t="shared" si="1"/>
-        <v>-1.4939969883648985E-2</v>
-      </c>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F21" s="3" t="s">
         <v>43</v>
       </c>
@@ -6639,676 +6372,935 @@
         <v>0.91989987484355396</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C22"/>
       <c r="D22"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="F24" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24"/>
+      <c r="K24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="J25"/>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B26" s="5">
+        <v>0.94074074074073999</v>
+      </c>
+      <c r="C26" s="7">
+        <f>B26-G3</f>
+        <v>0.22109117878829998</v>
+      </c>
+      <c r="D26" s="7">
+        <f>B26-M3</f>
+        <v>7.3245916724177018E-2</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="5">
         <v>0.70833333333333304</v>
       </c>
-      <c r="C25" s="7">
-        <f>B25-G3</f>
+      <c r="H26" s="7">
+        <f>G26-G3</f>
         <v>-1.1316228619106972E-2</v>
       </c>
-      <c r="D25" s="7">
-        <f>B25-J3</f>
+      <c r="I26" s="7">
+        <f>G26-J3</f>
         <v>-3.6059907834100957E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="J26"/>
+      <c r="K26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="5">
+        <v>0.91455273698264306</v>
+      </c>
+      <c r="M26" s="7">
+        <f>L26-M3</f>
+        <v>4.7057912966080084E-2</v>
+      </c>
+      <c r="N26" s="7">
+        <f>L26-J3</f>
+        <v>0.17015949581520906</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B27" s="5">
+        <v>0.60816326530612197</v>
+      </c>
+      <c r="C27" s="7">
+        <f>B27-G4</f>
+        <v>-1.683673469387803E-2</v>
+      </c>
+      <c r="D27" s="7">
+        <f>B27-M4</f>
+        <v>2.4829931972788932E-2</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="5">
         <v>0.79220779220779203</v>
       </c>
-      <c r="C26" s="7">
-        <f t="shared" ref="C26:C43" si="2">B26-G4</f>
+      <c r="H27" s="7">
+        <f>G27-G4</f>
         <v>0.16720779220779203</v>
       </c>
-      <c r="D26" s="7">
-        <f t="shared" ref="D26:D43" si="3">B26-J4</f>
+      <c r="I27" s="7">
+        <f>G27-J4</f>
         <v>-4.1866934761949359E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="J27"/>
+      <c r="K27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0.82683982683982604</v>
+      </c>
+      <c r="M27" s="7">
+        <f>L27-M4</f>
+        <v>0.243506493506493</v>
+      </c>
+      <c r="N27" s="7">
+        <f>L27-J4</f>
+        <v>3.0445341155839079E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B28" s="5">
+        <v>0.81626794258373203</v>
+      </c>
+      <c r="C28" s="7">
+        <f>B28-G5</f>
+        <v>0.10138822770401801</v>
+      </c>
+      <c r="D28" s="7">
+        <f>B28-M5</f>
+        <v>0.30076122707701702</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="5">
         <v>0.71964956195244001</v>
       </c>
-      <c r="C27" s="7">
-        <f t="shared" si="2"/>
+      <c r="H28" s="7">
+        <f>G28-G5</f>
         <v>4.7698470727259856E-3</v>
       </c>
-      <c r="D27" s="7">
-        <f t="shared" si="3"/>
+      <c r="I28" s="7">
+        <f>G28-J5</f>
         <v>0.18885777309613505</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="J28"/>
+      <c r="K28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0.49951124144672499</v>
+      </c>
+      <c r="M28" s="7">
+        <f>L28-M5</f>
+        <v>-1.5995474059990022E-2</v>
+      </c>
+      <c r="N28" s="7">
+        <f>L28-J5</f>
+        <v>-3.1280547409579973E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B29" s="5">
+        <v>0.85029239766081799</v>
+      </c>
+      <c r="C29" s="7">
+        <f>B29-G6</f>
+        <v>0.40089968511021101</v>
+      </c>
+      <c r="D29" s="7">
+        <f>B29-M6</f>
+        <v>-4.2530568846360639E-3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="5">
         <v>0.34117647058823503</v>
       </c>
-      <c r="C28" s="7">
-        <f t="shared" si="2"/>
+      <c r="H29" s="7">
+        <f>G29-G6</f>
         <v>-0.10821624196237195</v>
       </c>
-      <c r="D28" s="7">
-        <f t="shared" si="3"/>
+      <c r="I29" s="7">
+        <f>G29-J6</f>
         <v>-2.828165749058198E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="J29"/>
+      <c r="K29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="M29" s="7">
+        <f>L29-M6</f>
+        <v>2.0454545454545947E-2</v>
+      </c>
+      <c r="N29" s="7">
+        <f>L29-J6</f>
+        <v>0.50554187192118305</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B30" s="5">
+        <v>0.90588235294117603</v>
+      </c>
+      <c r="C30" s="7">
+        <f>B30-G7</f>
+        <v>5.7182589347796076E-2</v>
+      </c>
+      <c r="D30" s="7">
+        <f>B30-M7</f>
+        <v>3.7164404223227976E-2</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="5">
         <v>0.75553857906799005</v>
       </c>
-      <c r="C29" s="7">
-        <f t="shared" si="2"/>
+      <c r="H30" s="7">
+        <f>G30-G7</f>
         <v>-9.3161184525389906E-2</v>
       </c>
-      <c r="D29" s="7">
-        <f t="shared" si="3"/>
+      <c r="I30" s="7">
+        <f>G30-J7</f>
         <v>-0.15475017899200394</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="J30"/>
+      <c r="K30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0.80780780780780703</v>
+      </c>
+      <c r="M30" s="7">
+        <f>L30-M7</f>
+        <v>-6.091014091014102E-2</v>
+      </c>
+      <c r="N30" s="7">
+        <f>L30-J7</f>
+        <v>-0.10248095025218695</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B31" s="5">
+        <v>0.79937304075235105</v>
+      </c>
+      <c r="C31" s="7">
+        <f>B31-G8</f>
+        <v>0.17264981699837501</v>
+      </c>
+      <c r="D31" s="7">
+        <f>B31-M8</f>
+        <v>-2.2849181469870916E-2</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="5">
         <v>0.65280289330922203</v>
       </c>
-      <c r="C30" s="7">
-        <f t="shared" si="2"/>
+      <c r="H31" s="7">
+        <f>G31-G8</f>
         <v>2.6079669555245988E-2</v>
       </c>
-      <c r="D30" s="7">
-        <f t="shared" si="3"/>
+      <c r="I31" s="7">
+        <f>G31-J8</f>
         <v>0.12553016603649503</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="J31"/>
+      <c r="K31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.76149068322981295</v>
+      </c>
+      <c r="M31" s="7">
+        <f>L31-M8</f>
+        <v>-6.0731538992409018E-2</v>
+      </c>
+      <c r="N31" s="7">
+        <f>L31-J8</f>
+        <v>0.23421795595708594</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B32" s="5">
+        <v>0.75969962453066298</v>
+      </c>
+      <c r="C32" s="7">
+        <f>B32-G9</f>
+        <v>0.26491989445681596</v>
+      </c>
+      <c r="D32" s="7">
+        <f>B32-M9</f>
+        <v>-8.4163174983220568E-3</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="5">
         <v>0.606976172930483</v>
       </c>
-      <c r="C31" s="7">
-        <f t="shared" si="2"/>
+      <c r="H32" s="7">
+        <f>G32-G9</f>
         <v>0.11219644285663599</v>
       </c>
-      <c r="D31" s="7">
-        <f t="shared" si="3"/>
+      <c r="I32" s="7">
+        <f>G32-J9</f>
         <v>6.1099001411031972E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="J32"/>
+      <c r="K32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.68831168831168799</v>
+      </c>
+      <c r="M32" s="7">
+        <f>L32-M9</f>
+        <v>-7.9804253717297047E-2</v>
+      </c>
+      <c r="N32" s="7">
+        <f>L32-J9</f>
+        <v>0.14243451679223695</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B33" s="5">
+        <v>0.94871794871794801</v>
+      </c>
+      <c r="C33" s="7">
+        <f>B33-G10</f>
+        <v>0.25373617131396797</v>
+      </c>
+      <c r="D33" s="7">
+        <f>B33-M10</f>
+        <v>0.38986322973597598</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="5">
         <v>0.69498177740398004</v>
       </c>
-      <c r="C32" s="7">
-        <f t="shared" si="2"/>
+      <c r="H33" s="7">
+        <f>G33-G10</f>
         <v>0</v>
       </c>
-      <c r="D32" s="7">
-        <f t="shared" si="3"/>
+      <c r="I33" s="7">
+        <f>G33-J10</f>
         <v>-3.9328356906153994E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="J33"/>
+      <c r="K33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.52492046659597003</v>
+      </c>
+      <c r="M33" s="7">
+        <f>L33-M10</f>
+        <v>-3.3934252386002006E-2</v>
+      </c>
+      <c r="N33" s="7">
+        <f>L33-J10</f>
+        <v>-0.20938966771416401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B34" s="5">
+        <v>0.68058838980824699</v>
+      </c>
+      <c r="C34" s="7">
+        <f>B34-G11</f>
+        <v>2.4338389808246985E-2</v>
+      </c>
+      <c r="D34" s="7">
+        <f>B34-M11</f>
+        <v>7.861117080975033E-3</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="5">
         <v>0.63841807909604498</v>
       </c>
-      <c r="C33" s="7">
-        <f t="shared" si="2"/>
+      <c r="H34" s="7">
+        <f>G34-G11</f>
         <v>-1.7831920903955023E-2</v>
       </c>
-      <c r="D33" s="7">
-        <f t="shared" si="3"/>
+      <c r="I34" s="7">
+        <f>G34-J11</f>
         <v>0.12424803861021594</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="J34"/>
+      <c r="K34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.74439324116743399</v>
+      </c>
+      <c r="M34" s="7">
+        <f>L34-M11</f>
+        <v>7.1665968440162042E-2</v>
+      </c>
+      <c r="N34" s="7">
+        <f>L34-J11</f>
+        <v>0.23022320068160496</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="5">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7">
-        <f t="shared" si="2"/>
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="C35" s="7">
+        <f>B35-G12</f>
         <v>0</v>
       </c>
-      <c r="D34" s="7">
-        <f t="shared" si="3"/>
+      <c r="D35" s="7">
+        <f>B35-M12</f>
         <v>2.1283671433322993E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="F35" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1</v>
+      </c>
+      <c r="H35" s="7">
+        <f>G35-G12</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="7">
+        <f>G35-J12</f>
+        <v>2.1283671433322993E-2</v>
+      </c>
+      <c r="J35"/>
+      <c r="K35" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.97871632856667701</v>
+      </c>
+      <c r="M35" s="7">
+        <f>L35-M12</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="7">
+        <f>L35-J12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="C35" s="7">
-        <f t="shared" si="2"/>
+      <c r="B36" s="5">
+        <v>1</v>
+      </c>
+      <c r="C36" s="7">
+        <f>B36-G13</f>
         <v>0</v>
       </c>
-      <c r="D35" s="7">
-        <f t="shared" si="3"/>
+      <c r="D36" s="7">
+        <f>B36-M13</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="F36" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="5">
+        <v>1</v>
+      </c>
+      <c r="H36" s="7">
+        <f>G36-G13</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="7">
+        <f>G36-J13</f>
+        <v>0</v>
+      </c>
+      <c r="J36"/>
+      <c r="K36" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1</v>
+      </c>
+      <c r="M36" s="7">
+        <f>L36-M13</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="7">
+        <f>L36-J13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B37" s="5">
+        <v>0.61904761904761896</v>
+      </c>
+      <c r="C37" s="7">
+        <f>B37-G14</f>
+        <v>7.1274961597542985E-2</v>
+      </c>
+      <c r="D37" s="7">
+        <f>B37-M14</f>
+        <v>0.11596863645056499</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="5">
         <v>0.40427672955974803</v>
       </c>
-      <c r="C36" s="7">
-        <f t="shared" si="2"/>
+      <c r="H37" s="7">
+        <f>G37-G14</f>
         <v>-0.14349592789032795</v>
       </c>
-      <c r="D36" s="7">
-        <f t="shared" si="3"/>
+      <c r="I37" s="7">
+        <f>G37-J14</f>
         <v>0.15427672955974803</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="J37"/>
+      <c r="K37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.694902823615694</v>
+      </c>
+      <c r="M37" s="7">
+        <f>L37-M14</f>
+        <v>0.19182384101864003</v>
+      </c>
+      <c r="N37" s="7">
+        <f>L37-J14</f>
+        <v>0.444902823615694</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="C38" s="7">
+        <f>B38-G15</f>
+        <v>0.10174880763116101</v>
+      </c>
+      <c r="D38" s="7">
+        <f>B38-M15</f>
+        <v>3.7758112094395946E-2</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G38" s="5">
         <v>0.89825119236883899</v>
       </c>
-      <c r="C37" s="7">
-        <f t="shared" si="2"/>
+      <c r="H38" s="7">
+        <f>G38-G15</f>
         <v>0</v>
       </c>
-      <c r="D37" s="7">
-        <f t="shared" si="3"/>
+      <c r="I38" s="7">
+        <f>G38-J15</f>
         <v>2.7544121661769005E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="J38"/>
+      <c r="K38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.96224188790560405</v>
+      </c>
+      <c r="M38" s="7">
+        <f>L38-M15</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="7">
+        <f>L38-J15</f>
+        <v>9.1534817198534069E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B39" s="5">
+        <v>0.89825119236883899</v>
+      </c>
+      <c r="C39" s="7">
+        <f>B39-G16</f>
+        <v>-6.7832538420773969E-2</v>
+      </c>
+      <c r="D39" s="7">
+        <f>B39-M16</f>
+        <v>-3.7102342984696057E-2</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="5">
         <v>0.92857142857142805</v>
       </c>
-      <c r="C38" s="7">
-        <f t="shared" si="2"/>
+      <c r="H39" s="7">
+        <f>G39-G16</f>
         <v>-3.7512302218184912E-2</v>
       </c>
-      <c r="D38" s="7">
-        <f t="shared" si="3"/>
+      <c r="I39" s="7">
+        <f>G39-J16</f>
         <v>-3.7512302218184912E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="J39"/>
+      <c r="K39" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.89825119236883899</v>
+      </c>
+      <c r="M39" s="7">
+        <f>L39-M16</f>
+        <v>-3.7102342984696057E-2</v>
+      </c>
+      <c r="N39" s="7">
+        <f>L39-J16</f>
+        <v>-6.7832538420773969E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B40" s="5">
+        <v>0.73569321533923304</v>
+      </c>
+      <c r="C40" s="7">
+        <f>B40-G17</f>
+        <v>5.6093715965016E-2</v>
+      </c>
+      <c r="D40" s="7">
+        <f>B40-M17</f>
+        <v>-6.1476354125079569E-3</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G40" s="5">
         <v>0.554088742207554</v>
       </c>
-      <c r="C39" s="7">
-        <f t="shared" si="2"/>
+      <c r="H40" s="7">
+        <f>G40-G17</f>
         <v>-0.12551075716666305</v>
       </c>
-      <c r="D39" s="7">
-        <f t="shared" si="3"/>
+      <c r="I40" s="7">
+        <f>G40-J17</f>
         <v>-0.20621088326060999</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="J40"/>
+      <c r="K40" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.64444444444444404</v>
+      </c>
+      <c r="M40" s="7">
+        <f>L40-M17</f>
+        <v>-9.7396406307296957E-2</v>
+      </c>
+      <c r="N40" s="7">
+        <f>L40-J17</f>
+        <v>-0.11585518102371994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B41" s="5">
+        <v>0.65170068027210803</v>
+      </c>
+      <c r="C41" s="7">
+        <f>B41-G18</f>
+        <v>3.1964178076293037E-2</v>
+      </c>
+      <c r="D41" s="7">
+        <f>B41-M18</f>
+        <v>3.7824360513436073E-2</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G41" s="5">
         <v>0.60083160083160003</v>
       </c>
-      <c r="C40" s="7">
-        <f t="shared" si="2"/>
+      <c r="H41" s="7">
+        <f>G41-G18</f>
         <v>-1.8904901364214965E-2</v>
       </c>
-      <c r="D40" s="7">
-        <f t="shared" si="3"/>
+      <c r="I41" s="7">
+        <f>G41-J18</f>
         <v>7.0369080895396063E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="J41"/>
+      <c r="K41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.83959899749373401</v>
+      </c>
+      <c r="M41" s="7">
+        <f>L41-M18</f>
+        <v>0.22572267773506205</v>
+      </c>
+      <c r="N41" s="7">
+        <f>L41-J18</f>
+        <v>0.30913647755753004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B42" s="5">
+        <v>0.98099198099198104</v>
+      </c>
+      <c r="C42" s="7">
+        <f>B42-G19</f>
+        <v>6.4325314325315075E-2</v>
+      </c>
+      <c r="D42" s="7">
+        <f>B42-M19</f>
+        <v>3.8016038016038034E-2</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="5">
         <v>0.89792663476874002</v>
       </c>
-      <c r="C41" s="7">
-        <f t="shared" si="2"/>
+      <c r="H42" s="7">
+        <f>G42-G19</f>
         <v>-1.8740031897925946E-2</v>
       </c>
-      <c r="D41" s="7">
-        <f t="shared" si="3"/>
+      <c r="I42" s="7">
+        <f>G42-J19</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="J42"/>
+      <c r="K42" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.96257309941520397</v>
+      </c>
+      <c r="M42" s="7">
+        <f>L42-M19</f>
+        <v>1.9597156439260965E-2</v>
+      </c>
+      <c r="N42" s="7">
+        <f>L42-J19</f>
+        <v>6.4646464646463953E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B43" s="5">
+        <v>0.92727272727272703</v>
+      </c>
+      <c r="C43" s="7">
+        <f>B43-G20</f>
+        <v>-3.5300372142476943E-2</v>
+      </c>
+      <c r="D43" s="7">
+        <f>B43-M20</f>
+        <v>-1.5703215703215978E-2</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="5">
         <v>0.96456256921373196</v>
       </c>
-      <c r="C42" s="7">
-        <f t="shared" si="2"/>
+      <c r="H43" s="7">
+        <f>G43-G20</f>
         <v>1.9894697985279874E-3</v>
       </c>
-      <c r="D42" s="7">
-        <f t="shared" si="3"/>
+      <c r="I43" s="7">
+        <f>G43-J20</f>
         <v>1.9878040259540986E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="J43"/>
+      <c r="K43" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0.91028875805999399</v>
+      </c>
+      <c r="M43" s="7">
+        <f>L43-M20</f>
+        <v>-3.2687184915949019E-2</v>
+      </c>
+      <c r="N43" s="7">
+        <f>L43-J20</f>
+        <v>-3.4395770894196986E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B44" s="5">
+        <v>0.90495990495990497</v>
+      </c>
+      <c r="C44" s="7">
+        <f>B44-G21</f>
+        <v>0.14628720511073501</v>
+      </c>
+      <c r="D44" s="7">
+        <f>B44-M21</f>
+        <v>-1.4939969883648985E-2</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="5">
         <v>0.72331227136680998</v>
       </c>
-      <c r="C43" s="7">
-        <f t="shared" si="2"/>
+      <c r="H44" s="7">
+        <f>G44-G21</f>
         <v>-3.5360428482359985E-2</v>
       </c>
-      <c r="D43" s="7">
-        <f t="shared" si="3"/>
+      <c r="I44" s="7">
+        <f>G44-J21</f>
         <v>-2.4020143474750011E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C44"/>
-      <c r="D44"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="5">
-        <v>0.91455273698264306</v>
-      </c>
-      <c r="C47" s="7">
-        <f>B47-M3</f>
-        <v>4.7057912966080084E-2</v>
-      </c>
-      <c r="D47" s="7">
-        <f>B3-J3</f>
-        <v>0.19634749957330599</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" s="5">
-        <v>0.82683982683982604</v>
-      </c>
-      <c r="C48" s="7">
-        <f t="shared" ref="C48:C65" si="4">B48-M4</f>
-        <v>0.243506493506493</v>
-      </c>
-      <c r="D48" s="7">
-        <f t="shared" ref="D48:D65" si="5">B4-J4</f>
-        <v>-0.18823122037786499</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="5">
-        <v>0.49951124144672499</v>
-      </c>
-      <c r="C49" s="7">
-        <f t="shared" si="4"/>
-        <v>-1.5995474059990022E-2</v>
-      </c>
-      <c r="D49" s="7">
-        <f t="shared" si="5"/>
-        <v>0.28547615372742707</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B50" s="5">
-        <v>0.875</v>
-      </c>
-      <c r="C50" s="7">
-        <f t="shared" si="4"/>
-        <v>2.0454545454545947E-2</v>
-      </c>
-      <c r="D50" s="7">
-        <f t="shared" si="5"/>
-        <v>0.48083426958200098</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B51" s="5">
-        <v>0.80780780780780703</v>
-      </c>
-      <c r="C51" s="7">
-        <f t="shared" si="4"/>
-        <v>-6.091014091014102E-2</v>
-      </c>
-      <c r="D51" s="7">
-        <f t="shared" si="5"/>
-        <v>-4.4064051188179576E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" s="5">
-        <v>0.76149068322981295</v>
-      </c>
-      <c r="C52" s="7">
-        <f t="shared" si="4"/>
-        <v>-6.0731538992409018E-2</v>
-      </c>
-      <c r="D52" s="7">
-        <f t="shared" si="5"/>
-        <v>0.27210031347962405</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B53" s="5">
-        <v>0.68831168831168799</v>
-      </c>
-      <c r="C53" s="7">
-        <f t="shared" si="4"/>
-        <v>-7.9804253717297047E-2</v>
-      </c>
-      <c r="D53" s="7">
-        <f t="shared" si="5"/>
-        <v>0.21382245301121194</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B54" s="5">
-        <v>0.52492046659597003</v>
-      </c>
-      <c r="C54" s="7">
-        <f t="shared" si="4"/>
-        <v>-3.3934252386002006E-2</v>
-      </c>
-      <c r="D54" s="7">
-        <f t="shared" si="5"/>
-        <v>0.21440781440781398</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B55" s="5">
-        <v>0.74439324116743399</v>
-      </c>
-      <c r="C55" s="7">
-        <f t="shared" si="4"/>
-        <v>7.1665968440162042E-2</v>
-      </c>
-      <c r="D55" s="7">
-        <f t="shared" si="5"/>
-        <v>0.16641834932241795</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="5">
-        <v>0.97871632856667701</v>
-      </c>
-      <c r="C56" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D56" s="7">
-        <f t="shared" si="5"/>
-        <v>2.1283671433322993E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57" s="5">
-        <v>1</v>
-      </c>
-      <c r="C57" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D57" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="5">
-        <v>0.694902823615694</v>
-      </c>
-      <c r="C58" s="7">
-        <f t="shared" si="4"/>
-        <v>0.19182384101864003</v>
-      </c>
-      <c r="D58" s="7">
-        <f t="shared" si="5"/>
-        <v>0.36904761904761896</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5">
-        <v>0.96224188790560405</v>
-      </c>
-      <c r="C59" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="D59" s="7">
-        <f t="shared" si="5"/>
-        <v>0.12929292929293001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5">
-        <v>0.89825119236883899</v>
-      </c>
-      <c r="C60" s="7">
-        <f t="shared" si="4"/>
-        <v>-3.7102342984696057E-2</v>
-      </c>
-      <c r="D60" s="7">
-        <f t="shared" si="5"/>
-        <v>-6.7832538420773969E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5">
-        <v>0.64444444444444404</v>
-      </c>
-      <c r="C61" s="7">
-        <f t="shared" si="4"/>
-        <v>-9.7396406307296957E-2</v>
-      </c>
-      <c r="D61" s="7">
-        <f t="shared" si="5"/>
-        <v>-2.4606410128930944E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5">
-        <v>0.83959899749373401</v>
-      </c>
-      <c r="C62" s="7">
-        <f t="shared" si="4"/>
-        <v>0.22572267773506205</v>
-      </c>
-      <c r="D62" s="7">
-        <f t="shared" si="5"/>
-        <v>0.12123816033590407</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5">
-        <v>0.96257309941520397</v>
-      </c>
-      <c r="C63" s="7">
-        <f t="shared" si="4"/>
-        <v>1.9597156439260965E-2</v>
-      </c>
-      <c r="D63" s="7">
-        <f t="shared" si="5"/>
-        <v>8.3065346223241021E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5">
-        <v>0.91028875805999399</v>
-      </c>
-      <c r="C64" s="7">
-        <f t="shared" si="4"/>
-        <v>-3.2687184915949019E-2</v>
-      </c>
-      <c r="D64" s="7">
-        <f t="shared" si="5"/>
-        <v>-1.7411801681463945E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="J44"/>
+      <c r="K44" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B65" s="5">
+      <c r="L44" s="5">
         <v>0.90780754825698595</v>
       </c>
-      <c r="C65" s="7">
-        <f t="shared" si="4"/>
+      <c r="M44" s="7">
+        <f>L44-M21</f>
         <v>-1.2092326586568003E-2</v>
       </c>
-      <c r="D65" s="7">
-        <f t="shared" si="5"/>
-        <v>0.17924561924561999</v>
+      <c r="N44" s="7">
+        <f>L44-J21</f>
+        <v>0.18209326254270097</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="K24:N24"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:A21 H1:I1 K1:L1 G23:M1048576 G2:M21">
+  <conditionalFormatting sqref="A25:A44 H1:I1 K1:L1 G2:M21 G45:M1048576 L24:N44">
     <cfRule type="colorScale" priority="43">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7320,7 +7312,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:A43">
+  <conditionalFormatting sqref="F25:F44">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7332,7 +7324,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46:A65">
+  <conditionalFormatting sqref="K25:K44">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7344,7 +7336,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B21">
+  <conditionalFormatting sqref="B26:B44">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7356,7 +7348,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B43">
+  <conditionalFormatting sqref="G26:G44">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7368,7 +7360,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B65">
+  <conditionalFormatting sqref="L26:L44">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7380,7 +7372,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:D1 C3:D21 C23:D23 C25:D43 C45:D45 C47:D65 C1591:D1048576">
+  <conditionalFormatting sqref="C24:D24 C26:D44 H24:I24 H26:I44 M24:N24 C1591:D1048576 M26:N44">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
